--- a/db/data/office_items.xlsx
+++ b/db/data/office_items.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CBEEEA-BF86-40E8-878D-36E9A7DB3236}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{87A25D13-B481-4D37-BAE3-1CC2A95C2B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="405">
   <si>
     <t>temp_id</t>
   </si>
@@ -213,12 +212,6 @@
     <t>साधारण हँसिया</t>
   </si>
   <si>
-    <t>Steel Drawer</t>
-  </si>
-  <si>
-    <t>स्टिल घर्रा</t>
-  </si>
-  <si>
     <t>Stove</t>
   </si>
   <si>
@@ -609,12 +602,6 @@
     <t>ग्यास सिलिण्डर</t>
   </si>
   <si>
-    <t>Narms 241</t>
-  </si>
-  <si>
-    <t>नार्म्स २४१</t>
-  </si>
-  <si>
     <t>Dalaf Sofa</t>
   </si>
   <si>
@@ -1234,12 +1221,36 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>Mahendra Scorpio Pickup</t>
+  </si>
+  <si>
+    <t>महेन्द्र स्कर्पियो पिक अप</t>
+  </si>
+  <si>
+    <t>LG Smart TV</t>
+  </si>
+  <si>
+    <t>एल जी स्मार्ट टिभी</t>
+  </si>
+  <si>
+    <t>Thermos</t>
+  </si>
+  <si>
+    <t>थर्मस</t>
+  </si>
+  <si>
+    <t>Steel Cabinet</t>
+  </si>
+  <si>
+    <t>स्टिल दराज</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1592,8 +1603,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07017737-3195-4CF7-88A5-99496362B096}">
-  <dimension ref="A1:E205"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1604,7 +1615,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2019,10 +2030,10 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>403</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
@@ -2033,10 +2044,10 @@
         <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
@@ -2047,10 +2058,10 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
@@ -2061,10 +2072,10 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
@@ -2075,10 +2086,10 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
@@ -2089,10 +2100,10 @@
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
@@ -2103,10 +2114,10 @@
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
@@ -2117,10 +2128,10 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
@@ -2131,10 +2142,10 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
@@ -2145,10 +2156,10 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
@@ -2159,10 +2170,10 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
@@ -2173,10 +2184,10 @@
         <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
@@ -2187,10 +2198,10 @@
         <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
@@ -2201,10 +2212,10 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
@@ -2215,10 +2226,10 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
@@ -2229,10 +2240,10 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
@@ -2243,10 +2254,10 @@
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
@@ -2257,10 +2268,10 @@
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
@@ -2271,10 +2282,10 @@
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -2285,10 +2296,10 @@
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -2299,10 +2310,10 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -2313,10 +2324,10 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -2327,10 +2338,10 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E52" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -2341,10 +2352,10 @@
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -2355,10 +2366,10 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -2383,10 +2394,10 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
@@ -2397,10 +2408,10 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -2411,10 +2422,10 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
@@ -2425,10 +2436,10 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
@@ -2439,10 +2450,10 @@
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
@@ -2453,10 +2464,10 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
@@ -2467,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.25">
@@ -2481,10 +2492,10 @@
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E63" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
@@ -2495,10 +2506,10 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
@@ -2509,10 +2520,10 @@
         <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
@@ -2523,10 +2534,10 @@
         <v>5</v>
       </c>
       <c r="D66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
@@ -2537,10 +2548,10 @@
         <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
@@ -2551,10 +2562,10 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
@@ -2565,10 +2576,10 @@
         <v>24</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
@@ -2579,10 +2590,10 @@
         <v>19</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -2593,10 +2604,10 @@
         <v>34</v>
       </c>
       <c r="D71" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
@@ -2607,10 +2618,10 @@
         <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
@@ -2621,10 +2632,10 @@
         <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
@@ -2635,10 +2646,10 @@
         <v>25</v>
       </c>
       <c r="D74" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
@@ -2649,10 +2660,10 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
@@ -2663,10 +2674,10 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.25">
@@ -2677,10 +2688,10 @@
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
@@ -2691,10 +2702,10 @@
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.25">
@@ -2705,10 +2716,10 @@
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.25">
@@ -2719,10 +2730,10 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.25">
@@ -2733,10 +2744,10 @@
         <v>29</v>
       </c>
       <c r="D81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.25">
@@ -2747,10 +2758,10 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E82" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -2761,10 +2772,10 @@
         <v>29</v>
       </c>
       <c r="D83" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E83" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.25">
@@ -2775,10 +2786,10 @@
         <v>29</v>
       </c>
       <c r="D84" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.25">
@@ -2789,10 +2800,10 @@
         <v>29</v>
       </c>
       <c r="D85" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E85" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.25">
@@ -2803,10 +2814,10 @@
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E86" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.25">
@@ -2817,10 +2828,10 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E87" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.25">
@@ -2831,10 +2842,10 @@
         <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E88" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
@@ -2845,10 +2856,10 @@
         <v>8</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.25">
@@ -2859,10 +2870,10 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E90" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.25">
@@ -2873,10 +2884,10 @@
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E91" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.25">
@@ -2887,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E92" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.25">
@@ -2901,10 +2912,10 @@
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E93" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
@@ -2915,10 +2926,10 @@
         <v>8</v>
       </c>
       <c r="D94" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
@@ -2929,10 +2940,10 @@
         <v>32</v>
       </c>
       <c r="D95" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.25">
@@ -2943,10 +2954,10 @@
         <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E96" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
@@ -2957,10 +2968,10 @@
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
@@ -2971,10 +2982,10 @@
         <v>34</v>
       </c>
       <c r="D98" t="s">
-        <v>192</v>
+        <v>401</v>
       </c>
       <c r="E98" t="s">
-        <v>193</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
@@ -2985,10 +2996,10 @@
         <v>65</v>
       </c>
       <c r="D99" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E99" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
@@ -2999,10 +3010,10 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E100" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.25">
@@ -3013,10 +3024,10 @@
         <v>4</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E101" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.25">
@@ -3027,10 +3038,10 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E102" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
@@ -3041,10 +3052,10 @@
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E103" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
@@ -3055,10 +3066,10 @@
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
@@ -3069,10 +3080,10 @@
         <v>37</v>
       </c>
       <c r="D105" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E105" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
@@ -3083,10 +3094,10 @@
         <v>5</v>
       </c>
       <c r="D106" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.25">
@@ -3097,10 +3108,10 @@
         <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E107" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
@@ -3111,10 +3122,10 @@
         <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E108" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.25">
@@ -3125,10 +3136,10 @@
         <v>8</v>
       </c>
       <c r="D109" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E109" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
@@ -3139,10 +3150,10 @@
         <v>36</v>
       </c>
       <c r="D110" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E110" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
@@ -3153,10 +3164,10 @@
         <v>4</v>
       </c>
       <c r="D111" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E111" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
@@ -3167,10 +3178,10 @@
         <v>34</v>
       </c>
       <c r="D112" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E112" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.25">
@@ -3181,10 +3192,10 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E113" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.25">
@@ -3195,10 +3206,10 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E114" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.25">
@@ -3209,10 +3220,10 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E115" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.25">
@@ -3223,10 +3234,10 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E116" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.25">
@@ -3237,10 +3248,10 @@
         <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.25">
@@ -3251,10 +3262,10 @@
         <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E118" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.25">
@@ -3265,10 +3276,10 @@
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E119" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.25">
@@ -3279,10 +3290,10 @@
         <v>8</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E120" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.25">
@@ -3293,10 +3304,10 @@
         <v>27</v>
       </c>
       <c r="D121" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E121" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.25">
@@ -3307,10 +3318,10 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E122" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.25">
@@ -3321,10 +3332,10 @@
         <v>37</v>
       </c>
       <c r="D123" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E123" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.25">
@@ -3335,10 +3346,10 @@
         <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E124" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.25">
@@ -3349,10 +3360,10 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E125" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.25">
@@ -3363,10 +3374,10 @@
         <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E126" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.25">
@@ -3377,10 +3388,10 @@
         <v>60</v>
       </c>
       <c r="D127" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E127" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.25">
@@ -3391,10 +3402,10 @@
         <v>34</v>
       </c>
       <c r="D128" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E128" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
@@ -3405,10 +3416,10 @@
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E129" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
@@ -3419,10 +3430,10 @@
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E130" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
@@ -3433,10 +3444,10 @@
         <v>65</v>
       </c>
       <c r="D131" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E131" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.25">
@@ -3447,10 +3458,10 @@
         <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E132" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.25">
@@ -3461,10 +3472,10 @@
         <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E133" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.25">
@@ -3475,10 +3486,10 @@
         <v>4</v>
       </c>
       <c r="D134" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E134" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.25">
@@ -3489,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.25">
@@ -3503,10 +3514,10 @@
         <v>34</v>
       </c>
       <c r="D136" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E136" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.25">
@@ -3517,10 +3528,10 @@
         <v>2</v>
       </c>
       <c r="D137" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E137" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.25">
@@ -3531,10 +3542,10 @@
         <v>36</v>
       </c>
       <c r="D138" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E138" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.25">
@@ -3545,10 +3556,10 @@
         <v>38</v>
       </c>
       <c r="D139" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E139" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.25">
@@ -3559,10 +3570,10 @@
         <v>39</v>
       </c>
       <c r="D140" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E140" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.25">
@@ -3573,10 +3584,10 @@
         <v>34</v>
       </c>
       <c r="D141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E141" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.25">
@@ -3587,10 +3598,10 @@
         <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E142" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.25">
@@ -3601,10 +3612,10 @@
         <v>28</v>
       </c>
       <c r="D143" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.25">
@@ -3615,10 +3626,10 @@
         <v>37</v>
       </c>
       <c r="D144" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E144" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.25">
@@ -3629,10 +3640,10 @@
         <v>16</v>
       </c>
       <c r="D145" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E145" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.25">
@@ -3643,10 +3654,10 @@
         <v>5</v>
       </c>
       <c r="D146" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E146" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.25">
@@ -3657,10 +3668,10 @@
         <v>11</v>
       </c>
       <c r="D147" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E147" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.25">
@@ -3671,10 +3682,10 @@
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E148" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.25">
@@ -3685,10 +3696,10 @@
         <v>40</v>
       </c>
       <c r="D149" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E149" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.25">
@@ -3699,10 +3710,10 @@
         <v>40</v>
       </c>
       <c r="D150" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E150" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.25">
@@ -3713,10 +3724,10 @@
         <v>40</v>
       </c>
       <c r="D151" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E151" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.25">
@@ -3727,10 +3738,10 @@
         <v>35</v>
       </c>
       <c r="D152" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E152" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.25">
@@ -3741,10 +3752,10 @@
         <v>3</v>
       </c>
       <c r="D153" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E153" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.25">
@@ -3755,10 +3766,10 @@
         <v>34</v>
       </c>
       <c r="D154" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E154" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.25">
@@ -3769,10 +3780,10 @@
         <v>41</v>
       </c>
       <c r="D155" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E155" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.25">
@@ -3783,10 +3794,10 @@
         <v>34</v>
       </c>
       <c r="D156" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E156" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.25">
@@ -3797,10 +3808,10 @@
         <v>34</v>
       </c>
       <c r="D157" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E157" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.25">
@@ -3811,10 +3822,10 @@
         <v>34</v>
       </c>
       <c r="D158" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E158" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.25">
@@ -3825,10 +3836,10 @@
         <v>4</v>
       </c>
       <c r="D159" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E159" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.25">
@@ -3839,10 +3850,10 @@
         <v>31</v>
       </c>
       <c r="D160" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E160" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.25">
@@ -3853,10 +3864,10 @@
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E161" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.25">
@@ -3867,10 +3878,10 @@
         <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E162" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.25">
@@ -3881,10 +3892,10 @@
         <v>13</v>
       </c>
       <c r="D163" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E163" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.25">
@@ -3895,10 +3906,10 @@
         <v>30</v>
       </c>
       <c r="D164" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E164" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.25">
@@ -3909,10 +3920,10 @@
         <v>3</v>
       </c>
       <c r="D165" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E165" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.25">
@@ -3923,10 +3934,10 @@
         <v>42</v>
       </c>
       <c r="D166" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E166" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.25">
@@ -3937,10 +3948,10 @@
         <v>3</v>
       </c>
       <c r="D167" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E167" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.25">
@@ -3951,10 +3962,10 @@
         <v>16</v>
       </c>
       <c r="D168" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E168" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.25">
@@ -3965,10 +3976,10 @@
         <v>43</v>
       </c>
       <c r="D169" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E169" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.25">
@@ -3979,10 +3990,10 @@
         <v>27</v>
       </c>
       <c r="D170" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E170" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.25">
@@ -3993,10 +4004,10 @@
         <v>14</v>
       </c>
       <c r="D171" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E171" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.25">
@@ -4007,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E172" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.25">
@@ -4021,10 +4032,10 @@
         <v>44</v>
       </c>
       <c r="D173" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E173" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.25">
@@ -4035,10 +4046,10 @@
         <v>65</v>
       </c>
       <c r="D174" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E174" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.25">
@@ -4049,10 +4060,10 @@
         <v>30</v>
       </c>
       <c r="D175" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E175" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.25">
@@ -4063,10 +4074,10 @@
         <v>4</v>
       </c>
       <c r="D176" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E176" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.25">
@@ -4077,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E177" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.25">
@@ -4091,10 +4102,10 @@
         <v>45</v>
       </c>
       <c r="D178" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E178" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.25">
@@ -4105,10 +4116,10 @@
         <v>46</v>
       </c>
       <c r="D179" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E179" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.25">
@@ -4119,10 +4130,10 @@
         <v>29</v>
       </c>
       <c r="D180" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E180" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.25">
@@ -4133,10 +4144,10 @@
         <v>37</v>
       </c>
       <c r="D181" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E181" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.25">
@@ -4147,10 +4158,10 @@
         <v>5</v>
       </c>
       <c r="D182" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E182" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.25">
@@ -4161,10 +4172,10 @@
         <v>7</v>
       </c>
       <c r="D183" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E183" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.25">
@@ -4175,10 +4186,10 @@
         <v>7</v>
       </c>
       <c r="D184" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E184" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.25">
@@ -4189,10 +4200,10 @@
         <v>47</v>
       </c>
       <c r="D185" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E185" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.25">
@@ -4203,10 +4214,10 @@
         <v>48</v>
       </c>
       <c r="D186" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E186" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.25">
@@ -4217,10 +4228,10 @@
         <v>22</v>
       </c>
       <c r="D187" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E187" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.25">
@@ -4231,10 +4242,10 @@
         <v>42</v>
       </c>
       <c r="D188" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E188" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.25">
@@ -4245,10 +4256,10 @@
         <v>49</v>
       </c>
       <c r="D189" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E189" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.25">
@@ -4259,10 +4270,10 @@
         <v>2</v>
       </c>
       <c r="D190" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E190" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.25">
@@ -4273,10 +4284,10 @@
         <v>50</v>
       </c>
       <c r="D191" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E191" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.25">
@@ -4287,10 +4298,10 @@
         <v>3</v>
       </c>
       <c r="D192" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E192" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.25">
@@ -4301,10 +4312,10 @@
         <v>39</v>
       </c>
       <c r="D193" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E193" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.25">
@@ -4315,10 +4326,10 @@
         <v>51</v>
       </c>
       <c r="D194" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E194" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.25">
@@ -4329,10 +4340,10 @@
         <v>34</v>
       </c>
       <c r="D195" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E195" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.25">
@@ -4343,10 +4354,10 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E196" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.25">
@@ -4357,10 +4368,10 @@
         <v>3</v>
       </c>
       <c r="D197" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E197" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.25">
@@ -4371,10 +4382,10 @@
         <v>32</v>
       </c>
       <c r="D198" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E198" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.25">
@@ -4385,10 +4396,10 @@
         <v>13</v>
       </c>
       <c r="D199" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E199" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.25">
@@ -4399,10 +4410,10 @@
         <v>33</v>
       </c>
       <c r="D200" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E200" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.25">
@@ -4413,10 +4424,10 @@
         <v>45</v>
       </c>
       <c r="D201" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E201" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.25">
@@ -4427,10 +4438,10 @@
         <v>52</v>
       </c>
       <c r="D202" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E202" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.25">
@@ -4441,10 +4452,10 @@
         <v>18</v>
       </c>
       <c r="D203" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E203" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.25">
@@ -4455,10 +4466,10 @@
         <v>53</v>
       </c>
       <c r="D204" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E204" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.25">
@@ -4469,10 +4480,38 @@
         <v>35</v>
       </c>
       <c r="D205" t="s">
+        <v>394</v>
+      </c>
+      <c r="E205" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B206" s="1">
+        <v>217</v>
+      </c>
+      <c r="C206" s="1">
+        <v>44</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E205" t="s">
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B207" s="1">
+        <v>218</v>
+      </c>
+      <c r="C207" s="1">
+        <v>48</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>399</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/db/data/office_items.xlsx
+++ b/db/data/office_items.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="623">
   <si>
     <t>temp_id</t>
   </si>
@@ -1245,6 +1245,660 @@
   </si>
   <si>
     <t>स्टिल दराज</t>
+  </si>
+  <si>
+    <t>item_classification_no</t>
+  </si>
+  <si>
+    <t>Photocopy Paper 70gms</t>
+  </si>
+  <si>
+    <t>Pilot Pen (Black)</t>
+  </si>
+  <si>
+    <t>Pilot Pen (Red)</t>
+  </si>
+  <si>
+    <t>Mobile Charger</t>
+  </si>
+  <si>
+    <t>index file</t>
+  </si>
+  <si>
+    <t>Ring file</t>
+  </si>
+  <si>
+    <t>Gel pen</t>
+  </si>
+  <si>
+    <t>Nepali paper</t>
+  </si>
+  <si>
+    <t>Record file</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>Harpic</t>
+  </si>
+  <si>
+    <t>Plate Board</t>
+  </si>
+  <si>
+    <t>Name Plate</t>
+  </si>
+  <si>
+    <t>Citizen Charter</t>
+  </si>
+  <si>
+    <t>Gift Karuwa</t>
+  </si>
+  <si>
+    <t>Silvar Cover</t>
+  </si>
+  <si>
+    <t>Gas Stove</t>
+  </si>
+  <si>
+    <t>Polyethelene Pipe</t>
+  </si>
+  <si>
+    <t>Bottle</t>
+  </si>
+  <si>
+    <t>Silver Karai</t>
+  </si>
+  <si>
+    <t>Spoon Big</t>
+  </si>
+  <si>
+    <t>Bowl</t>
+  </si>
+  <si>
+    <t>Spoon Small</t>
+  </si>
+  <si>
+    <t>Pendrive</t>
+  </si>
+  <si>
+    <t>Adaptor</t>
+  </si>
+  <si>
+    <t>Printer Cable</t>
+  </si>
+  <si>
+    <t>Telephone Cable</t>
+  </si>
+  <si>
+    <t>Cartidge</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Multiplug</t>
+  </si>
+  <si>
+    <t>Network Switch Plug</t>
+  </si>
+  <si>
+    <t>Key Board</t>
+  </si>
+  <si>
+    <t>Net Cable</t>
+  </si>
+  <si>
+    <t>Antivirus</t>
+  </si>
+  <si>
+    <t>Office Board</t>
+  </si>
+  <si>
+    <t>Cartidge Refill</t>
+  </si>
+  <si>
+    <t>HDMI cable</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Heating Unit</t>
+  </si>
+  <si>
+    <t>Phenile</t>
+  </si>
+  <si>
+    <t>Dot Pen</t>
+  </si>
+  <si>
+    <t>Binding Plastic</t>
+  </si>
+  <si>
+    <t>Dormat</t>
+  </si>
+  <si>
+    <t>Clip</t>
+  </si>
+  <si>
+    <t>Tipex</t>
+  </si>
+  <si>
+    <t>Gluestick</t>
+  </si>
+  <si>
+    <t>Marker Pen</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>File Rope</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Mesuring Tape</t>
+  </si>
+  <si>
+    <t>Pencil</t>
+  </si>
+  <si>
+    <t>Ereaser</t>
+  </si>
+  <si>
+    <t>Ma. Le. Pa. 52</t>
+  </si>
+  <si>
+    <t>Stamp</t>
+  </si>
+  <si>
+    <t>Tyre</t>
+  </si>
+  <si>
+    <t>Reject Box</t>
+  </si>
+  <si>
+    <t>Electric Jug</t>
+  </si>
+  <si>
+    <t>Dadu</t>
+  </si>
+  <si>
+    <t>Chopping Board</t>
+  </si>
+  <si>
+    <t>Steel Bata</t>
+  </si>
+  <si>
+    <t>Knife</t>
+  </si>
+  <si>
+    <t>Plate</t>
+  </si>
+  <si>
+    <t>Pressure Cooker</t>
+  </si>
+  <si>
+    <t>Rice Cooker</t>
+  </si>
+  <si>
+    <t>Mug</t>
+  </si>
+  <si>
+    <t>Heater</t>
+  </si>
+  <si>
+    <t>Cora Cloth</t>
+  </si>
+  <si>
+    <t>Zebra Jhola</t>
+  </si>
+  <si>
+    <t>Sirak</t>
+  </si>
+  <si>
+    <t>Dasana</t>
+  </si>
+  <si>
+    <t>Dari</t>
+  </si>
+  <si>
+    <t>Bed Cover</t>
+  </si>
+  <si>
+    <t>Sirak Cover</t>
+  </si>
+  <si>
+    <t>Sirani Cover</t>
+  </si>
+  <si>
+    <t>Electric Accessories</t>
+  </si>
+  <si>
+    <t>Laptop Battery</t>
+  </si>
+  <si>
+    <t>SMPS</t>
+  </si>
+  <si>
+    <t>Switch Port</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Roller</t>
+  </si>
+  <si>
+    <t>Brush</t>
+  </si>
+  <si>
+    <t>Panching Machine</t>
+  </si>
+  <si>
+    <t>Diary</t>
+  </si>
+  <si>
+    <t>Stapler</t>
+  </si>
+  <si>
+    <t>Tippani</t>
+  </si>
+  <si>
+    <t>Odonil</t>
+  </si>
+  <si>
+    <t>Ka. Sa. Mu. Form</t>
+  </si>
+  <si>
+    <t>M.B. Book</t>
+  </si>
+  <si>
+    <t>Masking Tape</t>
+  </si>
+  <si>
+    <t>Envalope (Kham)</t>
+  </si>
+  <si>
+    <t>Box File</t>
+  </si>
+  <si>
+    <t>Pen Stand</t>
+  </si>
+  <si>
+    <t>Bank Cash Book</t>
+  </si>
+  <si>
+    <t>Color Certificate</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>Lock and Key</t>
+  </si>
+  <si>
+    <t>binding Tape</t>
+  </si>
+  <si>
+    <t>Spiral Rod</t>
+  </si>
+  <si>
+    <t>Charging Battery</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>Courtain</t>
+  </si>
+  <si>
+    <t>Clamp Pipe</t>
+  </si>
+  <si>
+    <t>Carpet</t>
+  </si>
+  <si>
+    <t>Towel</t>
+  </si>
+  <si>
+    <t>Economic Law</t>
+  </si>
+  <si>
+    <t>Survey Reports</t>
+  </si>
+  <si>
+    <t>फोटोकपी पेपर ७० जीएमएस</t>
+  </si>
+  <si>
+    <t xml:space="preserve">पाइलट पेन कालो </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पाइलट पेन रातो </t>
+  </si>
+  <si>
+    <t>मोबाइल चार्जर</t>
+  </si>
+  <si>
+    <t>इन्डेक्स फाइल</t>
+  </si>
+  <si>
+    <t>रिङ्ग फाईल</t>
+  </si>
+  <si>
+    <t>जेल पेन</t>
+  </si>
+  <si>
+    <t>नेपाली कागज</t>
+  </si>
+  <si>
+    <t>रेकर्ड फाईल</t>
+  </si>
+  <si>
+    <t xml:space="preserve">रजिस्टर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">हर्पिक </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पानि तान्ने मोटर </t>
+  </si>
+  <si>
+    <t>प्लेट बोर्ड</t>
+  </si>
+  <si>
+    <t xml:space="preserve">भित्ते नेम प्लेट </t>
+  </si>
+  <si>
+    <t xml:space="preserve">नागरिक बडा पत्र </t>
+  </si>
+  <si>
+    <t xml:space="preserve">उपहार करुवा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">सिल्वर ढक्कन </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ग्यास चुलो </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पोलिथिन पाइप </t>
+  </si>
+  <si>
+    <t xml:space="preserve">बोतल </t>
+  </si>
+  <si>
+    <t>सिल्वर कराई</t>
+  </si>
+  <si>
+    <t xml:space="preserve">चम्चा ठुलो </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कचौरा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">चम्चा सानो </t>
+  </si>
+  <si>
+    <t>पेनड्राइभ</t>
+  </si>
+  <si>
+    <t>एडाप्टर</t>
+  </si>
+  <si>
+    <t>प्रिन्टर केबुल</t>
+  </si>
+  <si>
+    <t>टेलिफोन तार</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मोबाइल चार्जर </t>
+  </si>
+  <si>
+    <t>कार्टेज</t>
+  </si>
+  <si>
+    <t>र्याम</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मल्टिप्लग </t>
+  </si>
+  <si>
+    <t>नेटवर्क स्विच प्लग्</t>
+  </si>
+  <si>
+    <t xml:space="preserve">की बोर्ड </t>
+  </si>
+  <si>
+    <t xml:space="preserve">नेट तार </t>
+  </si>
+  <si>
+    <t xml:space="preserve">एन्टिभाइरस </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कार्यालय बोर्ड </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कार्टेज रिफिल </t>
+  </si>
+  <si>
+    <t>राउटर</t>
+  </si>
+  <si>
+    <t>Heating unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">फिनेल </t>
+  </si>
+  <si>
+    <t xml:space="preserve">डटपेन </t>
+  </si>
+  <si>
+    <t xml:space="preserve">बाइडीङ्ग प्लास्टिक </t>
+  </si>
+  <si>
+    <t>डोरम्याट</t>
+  </si>
+  <si>
+    <t xml:space="preserve">क्लिप </t>
+  </si>
+  <si>
+    <t>टिपेक्स</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ग्लुस्टिक </t>
+  </si>
+  <si>
+    <t xml:space="preserve">मार्कर पेन </t>
+  </si>
+  <si>
+    <t xml:space="preserve">स्केल </t>
+  </si>
+  <si>
+    <t xml:space="preserve">फाइल डोरी </t>
+  </si>
+  <si>
+    <t>क्यालकुलेटर</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मेजरिंग टेप </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पेन्सिल </t>
+  </si>
+  <si>
+    <t>इरेजर</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मा.ले.प.५२ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">प्लास्टिक कुर्चि </t>
+  </si>
+  <si>
+    <t>छाप</t>
+  </si>
+  <si>
+    <t xml:space="preserve">टायर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रेजेक्ट बक्स </t>
+  </si>
+  <si>
+    <t>इलेक्ट्रिक जग</t>
+  </si>
+  <si>
+    <t xml:space="preserve">डाडु </t>
+  </si>
+  <si>
+    <t xml:space="preserve">चपिंग बोर्ड </t>
+  </si>
+  <si>
+    <t xml:space="preserve">स्टिल बाटा </t>
+  </si>
+  <si>
+    <t>चक्कु</t>
+  </si>
+  <si>
+    <t>प्लेट</t>
+  </si>
+  <si>
+    <t xml:space="preserve">प्रेसर कुकर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">राइस कुकर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">स्टिल जुग </t>
+  </si>
+  <si>
+    <t xml:space="preserve">मग  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">हिटर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कोरा कपडा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">जेब्रा झोला </t>
+  </si>
+  <si>
+    <t xml:space="preserve">सिरक </t>
+  </si>
+  <si>
+    <t xml:space="preserve">डसना </t>
+  </si>
+  <si>
+    <t xml:space="preserve">दरि </t>
+  </si>
+  <si>
+    <t>तन्ना</t>
+  </si>
+  <si>
+    <t xml:space="preserve">सिरकको खोल </t>
+  </si>
+  <si>
+    <t>सिरानीको खोल</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ब्लान्केट </t>
+  </si>
+  <si>
+    <t xml:space="preserve">बिधुत मर्मत सामाग्रीहरु </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ल्यापटप ब्याट्री </t>
+  </si>
+  <si>
+    <t xml:space="preserve">स्वीच पोर्ट </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रंग </t>
+  </si>
+  <si>
+    <t xml:space="preserve">रोलर </t>
+  </si>
+  <si>
+    <t>ब्रश</t>
+  </si>
+  <si>
+    <t xml:space="preserve">पंचिंग  मेसिन </t>
+  </si>
+  <si>
+    <t xml:space="preserve">डायरि </t>
+  </si>
+  <si>
+    <t xml:space="preserve">स्टापलर मेसिन </t>
+  </si>
+  <si>
+    <t xml:space="preserve">टिप्पणि फाइल </t>
+  </si>
+  <si>
+    <t>ओडोनिल</t>
+  </si>
+  <si>
+    <t xml:space="preserve">क.स.मु. फारम </t>
+  </si>
+  <si>
+    <t>एम.बि.बुक</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मास्किम टेप </t>
+  </si>
+  <si>
+    <t xml:space="preserve">खाम </t>
+  </si>
+  <si>
+    <t xml:space="preserve">बक्स फाइल </t>
+  </si>
+  <si>
+    <t>पेन स्ट्याण्ड</t>
+  </si>
+  <si>
+    <t xml:space="preserve">बैंक नगदी किताब </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कलर प्रमाणपत्र </t>
+  </si>
+  <si>
+    <t xml:space="preserve">झन्डा </t>
+  </si>
+  <si>
+    <t>ताला चाबी</t>
+  </si>
+  <si>
+    <t xml:space="preserve">वाईन्डीङ्ग टेप  </t>
+  </si>
+  <si>
+    <t>इस्पारल रड</t>
+  </si>
+  <si>
+    <t>चार्जिंग व्याट्री</t>
+  </si>
+  <si>
+    <t xml:space="preserve">चार्जर </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पर्दा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">क्ल्याम्प पाइप </t>
+  </si>
+  <si>
+    <t xml:space="preserve">कार्पेट </t>
+  </si>
+  <si>
+    <t>तौलिया</t>
+  </si>
+  <si>
+    <t>आर्थिक ऐन नियम संग्रह</t>
+  </si>
+  <si>
+    <t>सर्भे रिपोर्ट</t>
   </si>
 </sst>
 </file>
@@ -1604,16 +2258,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>396</v>
       </c>
@@ -1629,8 +2284,11 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
@@ -1643,8 +2301,11 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2</v>
       </c>
@@ -1657,8 +2318,11 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>3</v>
       </c>
@@ -1671,8 +2335,11 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>4</v>
       </c>
@@ -1685,8 +2352,11 @@
       <c r="E5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>5</v>
       </c>
@@ -1699,8 +2369,11 @@
       <c r="E6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>6</v>
       </c>
@@ -1713,8 +2386,11 @@
       <c r="E7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>7</v>
       </c>
@@ -1727,8 +2403,11 @@
       <c r="E8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>8</v>
       </c>
@@ -1741,8 +2420,11 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>9</v>
       </c>
@@ -1755,8 +2437,11 @@
       <c r="E10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>10</v>
       </c>
@@ -1769,8 +2454,11 @@
       <c r="E11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>11</v>
       </c>
@@ -1783,8 +2471,11 @@
       <c r="E12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>12</v>
       </c>
@@ -1797,8 +2488,11 @@
       <c r="E13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>13</v>
       </c>
@@ -1811,8 +2505,11 @@
       <c r="E14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>14</v>
       </c>
@@ -1825,8 +2522,11 @@
       <c r="E15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>15</v>
       </c>
@@ -1839,8 +2539,11 @@
       <c r="E16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>16</v>
       </c>
@@ -1853,8 +2556,11 @@
       <c r="E17" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>17</v>
       </c>
@@ -1867,8 +2573,11 @@
       <c r="E18" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>18</v>
       </c>
@@ -1881,8 +2590,11 @@
       <c r="E19" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>19</v>
       </c>
@@ -1895,8 +2607,11 @@
       <c r="E20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>20</v>
       </c>
@@ -1909,8 +2624,11 @@
       <c r="E21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>21</v>
       </c>
@@ -1923,8 +2641,11 @@
       <c r="E22" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>22</v>
       </c>
@@ -1937,8 +2658,11 @@
       <c r="E23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>23</v>
       </c>
@@ -1951,8 +2675,11 @@
       <c r="E24" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>24</v>
       </c>
@@ -1965,8 +2692,11 @@
       <c r="E25" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>25</v>
       </c>
@@ -1979,8 +2709,11 @@
       <c r="E26" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>26</v>
       </c>
@@ -1993,8 +2726,11 @@
       <c r="E27" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>27</v>
       </c>
@@ -2007,8 +2743,11 @@
       <c r="E28" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>28</v>
       </c>
@@ -2021,8 +2760,11 @@
       <c r="E29" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>29</v>
       </c>
@@ -2035,8 +2777,11 @@
       <c r="E30" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>30</v>
       </c>
@@ -2049,8 +2794,11 @@
       <c r="E31" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>31</v>
       </c>
@@ -2063,8 +2811,11 @@
       <c r="E32" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>32</v>
       </c>
@@ -2077,8 +2828,11 @@
       <c r="E33" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>33</v>
       </c>
@@ -2091,8 +2845,11 @@
       <c r="E34" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>34</v>
       </c>
@@ -2105,8 +2862,11 @@
       <c r="E35" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>35</v>
       </c>
@@ -2119,8 +2879,11 @@
       <c r="E36" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>36</v>
       </c>
@@ -2133,8 +2896,11 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>37</v>
       </c>
@@ -2147,8 +2913,11 @@
       <c r="E38" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>38</v>
       </c>
@@ -2161,8 +2930,11 @@
       <c r="E39" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>39</v>
       </c>
@@ -2175,8 +2947,11 @@
       <c r="E40" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>40</v>
       </c>
@@ -2189,8 +2964,11 @@
       <c r="E41" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>41</v>
       </c>
@@ -2203,8 +2981,11 @@
       <c r="E42" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>42</v>
       </c>
@@ -2217,8 +2998,11 @@
       <c r="E43" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>43</v>
       </c>
@@ -2231,8 +3015,11 @@
       <c r="E44" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>44</v>
       </c>
@@ -2245,8 +3032,11 @@
       <c r="E45" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>45</v>
       </c>
@@ -2259,8 +3049,11 @@
       <c r="E46" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>46</v>
       </c>
@@ -2273,8 +3066,11 @@
       <c r="E47" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>47</v>
       </c>
@@ -2287,8 +3083,11 @@
       <c r="E48" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>48</v>
       </c>
@@ -2301,8 +3100,11 @@
       <c r="E49" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>49</v>
       </c>
@@ -2315,8 +3117,11 @@
       <c r="E50" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>50</v>
       </c>
@@ -2329,8 +3134,11 @@
       <c r="E51" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>51</v>
       </c>
@@ -2343,8 +3151,11 @@
       <c r="E52" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>52</v>
       </c>
@@ -2357,8 +3168,11 @@
       <c r="E53" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>53</v>
       </c>
@@ -2371,8 +3185,11 @@
       <c r="E54" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>54</v>
       </c>
@@ -2385,8 +3202,11 @@
       <c r="E55" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>55</v>
       </c>
@@ -2399,8 +3219,11 @@
       <c r="E56" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>56</v>
       </c>
@@ -2413,8 +3236,11 @@
       <c r="E57" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>57</v>
       </c>
@@ -2427,8 +3253,11 @@
       <c r="E58" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>58</v>
       </c>
@@ -2441,8 +3270,11 @@
       <c r="E59" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>59</v>
       </c>
@@ -2455,8 +3287,11 @@
       <c r="E60" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>60</v>
       </c>
@@ -2469,8 +3304,11 @@
       <c r="E61" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>61</v>
       </c>
@@ -2483,8 +3321,11 @@
       <c r="E62" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>62</v>
       </c>
@@ -2497,8 +3338,11 @@
       <c r="E63" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>63</v>
       </c>
@@ -2511,8 +3355,11 @@
       <c r="E64" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>64</v>
       </c>
@@ -2525,8 +3372,11 @@
       <c r="E65" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>65</v>
       </c>
@@ -2539,8 +3389,11 @@
       <c r="E66" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>66</v>
       </c>
@@ -2553,8 +3406,11 @@
       <c r="E67" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>67</v>
       </c>
@@ -2567,8 +3423,11 @@
       <c r="E68" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>68</v>
       </c>
@@ -2581,8 +3440,11 @@
       <c r="E69" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>69</v>
       </c>
@@ -2595,8 +3457,11 @@
       <c r="E70" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>70</v>
       </c>
@@ -2609,8 +3474,11 @@
       <c r="E71" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>71</v>
       </c>
@@ -2623,8 +3491,11 @@
       <c r="E72" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>72</v>
       </c>
@@ -2637,8 +3508,11 @@
       <c r="E73" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>73</v>
       </c>
@@ -2651,8 +3525,11 @@
       <c r="E74" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>74</v>
       </c>
@@ -2665,8 +3542,11 @@
       <c r="E75" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>76</v>
       </c>
@@ -2679,8 +3559,11 @@
       <c r="E76" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>77</v>
       </c>
@@ -2693,8 +3576,11 @@
       <c r="E77" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>78</v>
       </c>
@@ -2707,8 +3593,11 @@
       <c r="E78" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>79</v>
       </c>
@@ -2721,8 +3610,11 @@
       <c r="E79" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>80</v>
       </c>
@@ -2735,8 +3627,11 @@
       <c r="E80" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>83</v>
       </c>
@@ -2749,8 +3644,11 @@
       <c r="E81" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>85</v>
       </c>
@@ -2763,8 +3661,11 @@
       <c r="E82" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>87</v>
       </c>
@@ -2777,8 +3678,11 @@
       <c r="E83" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>88</v>
       </c>
@@ -2791,8 +3695,11 @@
       <c r="E84" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>91</v>
       </c>
@@ -2805,8 +3712,11 @@
       <c r="E85" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>94</v>
       </c>
@@ -2819,8 +3729,11 @@
       <c r="E86" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>95</v>
       </c>
@@ -2833,8 +3746,11 @@
       <c r="E87" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>96</v>
       </c>
@@ -2847,8 +3763,11 @@
       <c r="E88" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>97</v>
       </c>
@@ -2861,8 +3780,11 @@
       <c r="E89" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>98</v>
       </c>
@@ -2875,8 +3797,11 @@
       <c r="E90" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>99</v>
       </c>
@@ -2889,8 +3814,11 @@
       <c r="E91" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92">
         <v>100</v>
       </c>
@@ -2903,8 +3831,11 @@
       <c r="E92" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>101</v>
       </c>
@@ -2917,8 +3848,11 @@
       <c r="E93" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94">
         <v>102</v>
       </c>
@@ -2931,8 +3865,11 @@
       <c r="E94" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95">
         <v>103</v>
       </c>
@@ -2945,8 +3882,11 @@
       <c r="E95" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96">
         <v>104</v>
       </c>
@@ -2959,8 +3899,11 @@
       <c r="E96" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97">
         <v>105</v>
       </c>
@@ -2973,8 +3916,11 @@
       <c r="E97" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98">
         <v>106</v>
       </c>
@@ -2987,8 +3933,11 @@
       <c r="E98" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99">
         <v>107</v>
       </c>
@@ -3001,8 +3950,11 @@
       <c r="E99" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100">
         <v>108</v>
       </c>
@@ -3015,8 +3967,11 @@
       <c r="E100" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101">
         <v>109</v>
       </c>
@@ -3029,8 +3984,11 @@
       <c r="E101" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102">
         <v>110</v>
       </c>
@@ -3043,8 +4001,11 @@
       <c r="E102" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103">
         <v>111</v>
       </c>
@@ -3057,8 +4018,11 @@
       <c r="E103" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104">
         <v>112</v>
       </c>
@@ -3071,8 +4035,11 @@
       <c r="E104" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105">
         <v>113</v>
       </c>
@@ -3085,8 +4052,11 @@
       <c r="E105" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106">
         <v>114</v>
       </c>
@@ -3099,8 +4069,11 @@
       <c r="E106" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107">
         <v>115</v>
       </c>
@@ -3113,8 +4086,11 @@
       <c r="E107" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108">
         <v>116</v>
       </c>
@@ -3127,8 +4103,11 @@
       <c r="E108" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109">
         <v>117</v>
       </c>
@@ -3141,8 +4120,11 @@
       <c r="E109" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110">
         <v>118</v>
       </c>
@@ -3155,8 +4137,11 @@
       <c r="E110" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F110">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B111">
         <v>119</v>
       </c>
@@ -3169,8 +4154,11 @@
       <c r="E111" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F111">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112">
         <v>120</v>
       </c>
@@ -3183,8 +4171,11 @@
       <c r="E112" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F112">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113">
         <v>121</v>
       </c>
@@ -3197,8 +4188,11 @@
       <c r="E113" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F113">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114">
         <v>122</v>
       </c>
@@ -3211,8 +4205,11 @@
       <c r="E114" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115">
         <v>123</v>
       </c>
@@ -3225,8 +4222,11 @@
       <c r="E115" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116">
         <v>124</v>
       </c>
@@ -3239,8 +4239,11 @@
       <c r="E116" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>125</v>
       </c>
@@ -3253,8 +4256,11 @@
       <c r="E117" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F117">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118">
         <v>126</v>
       </c>
@@ -3267,8 +4273,11 @@
       <c r="E118" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F118">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119">
         <v>127</v>
       </c>
@@ -3281,8 +4290,11 @@
       <c r="E119" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F119">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120">
         <v>128</v>
       </c>
@@ -3295,8 +4307,11 @@
       <c r="E120" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121">
         <v>129</v>
       </c>
@@ -3309,8 +4324,11 @@
       <c r="E121" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F121">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122">
         <v>130</v>
       </c>
@@ -3323,8 +4341,11 @@
       <c r="E122" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123">
         <v>131</v>
       </c>
@@ -3337,8 +4358,11 @@
       <c r="E123" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124">
         <v>132</v>
       </c>
@@ -3351,8 +4375,11 @@
       <c r="E124" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125">
         <v>133</v>
       </c>
@@ -3365,8 +4392,11 @@
       <c r="E125" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126">
         <v>134</v>
       </c>
@@ -3379,8 +4409,11 @@
       <c r="E126" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127">
         <v>135</v>
       </c>
@@ -3393,8 +4426,11 @@
       <c r="E127" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128">
         <v>136</v>
       </c>
@@ -3407,8 +4443,11 @@
       <c r="E128" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129">
         <v>137</v>
       </c>
@@ -3421,8 +4460,11 @@
       <c r="E129" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>138</v>
       </c>
@@ -3435,8 +4477,11 @@
       <c r="E130" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131">
         <v>139</v>
       </c>
@@ -3449,8 +4494,11 @@
       <c r="E131" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>140</v>
       </c>
@@ -3463,8 +4511,11 @@
       <c r="E132" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133">
         <v>141</v>
       </c>
@@ -3477,8 +4528,11 @@
       <c r="E133" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134">
         <v>142</v>
       </c>
@@ -3491,8 +4545,11 @@
       <c r="E134" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135">
         <v>143</v>
       </c>
@@ -3505,8 +4562,11 @@
       <c r="E135" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136">
         <v>144</v>
       </c>
@@ -3519,8 +4579,11 @@
       <c r="E136" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137">
         <v>145</v>
       </c>
@@ -3533,8 +4596,11 @@
       <c r="E137" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138">
         <v>146</v>
       </c>
@@ -3547,8 +4613,11 @@
       <c r="E138" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139">
         <v>147</v>
       </c>
@@ -3561,8 +4630,11 @@
       <c r="E139" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140">
         <v>148</v>
       </c>
@@ -3575,8 +4647,11 @@
       <c r="E140" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141">
         <v>149</v>
       </c>
@@ -3589,8 +4664,11 @@
       <c r="E141" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142">
         <v>150</v>
       </c>
@@ -3603,8 +4681,11 @@
       <c r="E142" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143">
         <v>151</v>
       </c>
@@ -3617,8 +4698,11 @@
       <c r="E143" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144">
         <v>152</v>
       </c>
@@ -3631,8 +4715,11 @@
       <c r="E144" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B145">
         <v>153</v>
       </c>
@@ -3645,8 +4732,11 @@
       <c r="E145" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B146">
         <v>154</v>
       </c>
@@ -3659,8 +4749,11 @@
       <c r="E146" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B147">
         <v>155</v>
       </c>
@@ -3673,8 +4766,11 @@
       <c r="E147" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148">
         <v>156</v>
       </c>
@@ -3687,8 +4783,11 @@
       <c r="E148" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B149">
         <v>157</v>
       </c>
@@ -3701,8 +4800,11 @@
       <c r="E149" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B150">
         <v>158</v>
       </c>
@@ -3715,8 +4817,11 @@
       <c r="E150" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151">
         <v>159</v>
       </c>
@@ -3729,8 +4834,11 @@
       <c r="E151" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B152">
         <v>160</v>
       </c>
@@ -3743,8 +4851,11 @@
       <c r="E152" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B153">
         <v>161</v>
       </c>
@@ -3757,8 +4868,11 @@
       <c r="E153" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F153">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B154">
         <v>162</v>
       </c>
@@ -3771,8 +4885,11 @@
       <c r="E154" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B155">
         <v>163</v>
       </c>
@@ -3785,8 +4902,11 @@
       <c r="E155" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F155">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156">
         <v>164</v>
       </c>
@@ -3799,8 +4919,11 @@
       <c r="E156" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B157">
         <v>165</v>
       </c>
@@ -3813,8 +4936,11 @@
       <c r="E157" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158">
         <v>166</v>
       </c>
@@ -3827,8 +4953,11 @@
       <c r="E158" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B159">
         <v>167</v>
       </c>
@@ -3841,8 +4970,11 @@
       <c r="E159" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B160">
         <v>168</v>
       </c>
@@ -3855,8 +4987,11 @@
       <c r="E160" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161">
         <v>169</v>
       </c>
@@ -3869,8 +5004,11 @@
       <c r="E161" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162">
         <v>170</v>
       </c>
@@ -3883,8 +5021,11 @@
       <c r="E162" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163">
         <v>171</v>
       </c>
@@ -3897,8 +5038,11 @@
       <c r="E163" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164">
         <v>172</v>
       </c>
@@ -3911,8 +5055,11 @@
       <c r="E164" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165">
         <v>173</v>
       </c>
@@ -3925,8 +5072,11 @@
       <c r="E165" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166">
         <v>174</v>
       </c>
@@ -3939,8 +5089,11 @@
       <c r="E166" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167">
         <v>175</v>
       </c>
@@ -3953,8 +5106,11 @@
       <c r="E167" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168">
         <v>176</v>
       </c>
@@ -3967,8 +5123,11 @@
       <c r="E168" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169">
         <v>177</v>
       </c>
@@ -3981,8 +5140,11 @@
       <c r="E169" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170">
         <v>178</v>
       </c>
@@ -3995,8 +5157,11 @@
       <c r="E170" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171">
         <v>179</v>
       </c>
@@ -4009,8 +5174,11 @@
       <c r="E171" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172">
         <v>180</v>
       </c>
@@ -4023,8 +5191,11 @@
       <c r="E172" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F172">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173">
         <v>181</v>
       </c>
@@ -4037,8 +5208,11 @@
       <c r="E173" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F173">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174">
         <v>182</v>
       </c>
@@ -4051,8 +5225,11 @@
       <c r="E174" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F174">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175">
         <v>183</v>
       </c>
@@ -4065,8 +5242,11 @@
       <c r="E175" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F175">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176">
         <v>184</v>
       </c>
@@ -4079,8 +5259,11 @@
       <c r="E176" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F176">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177">
         <v>185</v>
       </c>
@@ -4093,8 +5276,11 @@
       <c r="E177" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F177">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178">
         <v>186</v>
       </c>
@@ -4107,8 +5293,11 @@
       <c r="E178" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F178">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179">
         <v>187</v>
       </c>
@@ -4121,8 +5310,11 @@
       <c r="E179" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F179">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B180">
         <v>188</v>
       </c>
@@ -4135,8 +5327,11 @@
       <c r="E180" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F180">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B181">
         <v>189</v>
       </c>
@@ -4149,8 +5344,11 @@
       <c r="E181" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F181">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182">
         <v>190</v>
       </c>
@@ -4163,8 +5361,11 @@
       <c r="E182" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F182">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183">
         <v>191</v>
       </c>
@@ -4177,8 +5378,11 @@
       <c r="E183" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F183">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184">
         <v>192</v>
       </c>
@@ -4191,8 +5395,11 @@
       <c r="E184" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F184">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B185">
         <v>193</v>
       </c>
@@ -4205,8 +5412,11 @@
       <c r="E185" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F185">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186">
         <v>194</v>
       </c>
@@ -4219,8 +5429,11 @@
       <c r="E186" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F186">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187">
         <v>195</v>
       </c>
@@ -4233,8 +5446,11 @@
       <c r="E187" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F187">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188">
         <v>196</v>
       </c>
@@ -4247,8 +5463,11 @@
       <c r="E188" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F188">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189">
         <v>197</v>
       </c>
@@ -4261,8 +5480,11 @@
       <c r="E189" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F189">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190">
         <v>198</v>
       </c>
@@ -4275,8 +5497,11 @@
       <c r="E190" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F190">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191">
         <v>199</v>
       </c>
@@ -4289,8 +5514,11 @@
       <c r="E191" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F191">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192">
         <v>200</v>
       </c>
@@ -4303,8 +5531,11 @@
       <c r="E192" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F192">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B193">
         <v>203</v>
       </c>
@@ -4317,8 +5548,11 @@
       <c r="E193" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F193">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B194">
         <v>204</v>
       </c>
@@ -4331,8 +5565,11 @@
       <c r="E194" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F194">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195">
         <v>205</v>
       </c>
@@ -4345,8 +5582,11 @@
       <c r="E195" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F195">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196">
         <v>206</v>
       </c>
@@ -4359,8 +5599,11 @@
       <c r="E196" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F196">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197">
         <v>207</v>
       </c>
@@ -4373,8 +5616,11 @@
       <c r="E197" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F197">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198">
         <v>209</v>
       </c>
@@ -4387,8 +5633,11 @@
       <c r="E198" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F198">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199">
         <v>210</v>
       </c>
@@ -4401,8 +5650,11 @@
       <c r="E199" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F199">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200">
         <v>211</v>
       </c>
@@ -4415,8 +5667,11 @@
       <c r="E200" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F200">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201">
         <v>212</v>
       </c>
@@ -4429,8 +5684,11 @@
       <c r="E201" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F201">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B202">
         <v>213</v>
       </c>
@@ -4443,8 +5701,11 @@
       <c r="E202" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F202">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B203">
         <v>214</v>
       </c>
@@ -4457,8 +5718,11 @@
       <c r="E203" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F203">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B204">
         <v>215</v>
       </c>
@@ -4471,8 +5735,11 @@
       <c r="E204" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F204">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B205">
         <v>216</v>
       </c>
@@ -4485,8 +5752,11 @@
       <c r="E205" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F205">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B206" s="1">
         <v>217</v>
       </c>
@@ -4499,8 +5769,11 @@
       <c r="E206" s="1" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F206">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B207" s="1">
         <v>218</v>
       </c>
@@ -4512,6 +5785,1964 @@
       </c>
       <c r="E207" s="1" t="s">
         <v>400</v>
+      </c>
+      <c r="F207">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B208" s="1">
+        <v>219</v>
+      </c>
+      <c r="C208">
+        <v>62</v>
+      </c>
+      <c r="D208" t="s">
+        <v>406</v>
+      </c>
+      <c r="E208" t="s">
+        <v>513</v>
+      </c>
+      <c r="F208">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B209" s="1">
+        <v>220</v>
+      </c>
+      <c r="C209">
+        <v>54</v>
+      </c>
+      <c r="D209" t="s">
+        <v>407</v>
+      </c>
+      <c r="E209" t="s">
+        <v>514</v>
+      </c>
+      <c r="F209">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B210" s="1">
+        <v>221</v>
+      </c>
+      <c r="C210">
+        <v>54</v>
+      </c>
+      <c r="D210" t="s">
+        <v>408</v>
+      </c>
+      <c r="E210" t="s">
+        <v>515</v>
+      </c>
+      <c r="F210">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B211" s="1">
+        <v>222</v>
+      </c>
+      <c r="C211">
+        <v>34</v>
+      </c>
+      <c r="D211" t="s">
+        <v>409</v>
+      </c>
+      <c r="E211" t="s">
+        <v>516</v>
+      </c>
+      <c r="F211">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B212" s="1">
+        <v>223</v>
+      </c>
+      <c r="C212">
+        <v>21</v>
+      </c>
+      <c r="D212" t="s">
+        <v>410</v>
+      </c>
+      <c r="E212" t="s">
+        <v>517</v>
+      </c>
+      <c r="F212">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B213" s="1">
+        <v>224</v>
+      </c>
+      <c r="C213">
+        <v>21</v>
+      </c>
+      <c r="D213" t="s">
+        <v>411</v>
+      </c>
+      <c r="E213" t="s">
+        <v>518</v>
+      </c>
+      <c r="F213">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B214" s="1">
+        <v>225</v>
+      </c>
+      <c r="C214">
+        <v>54</v>
+      </c>
+      <c r="D214" t="s">
+        <v>412</v>
+      </c>
+      <c r="E214" t="s">
+        <v>519</v>
+      </c>
+      <c r="F214">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B215" s="1">
+        <v>226</v>
+      </c>
+      <c r="C215">
+        <v>62</v>
+      </c>
+      <c r="D215" t="s">
+        <v>413</v>
+      </c>
+      <c r="E215" t="s">
+        <v>520</v>
+      </c>
+      <c r="F215">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B216" s="1">
+        <v>227</v>
+      </c>
+      <c r="C216">
+        <v>21</v>
+      </c>
+      <c r="D216" t="s">
+        <v>414</v>
+      </c>
+      <c r="E216" t="s">
+        <v>521</v>
+      </c>
+      <c r="F216">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B217" s="1">
+        <v>228</v>
+      </c>
+      <c r="C217">
+        <v>61</v>
+      </c>
+      <c r="D217" t="s">
+        <v>415</v>
+      </c>
+      <c r="E217" t="s">
+        <v>522</v>
+      </c>
+      <c r="F217">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B218" s="1">
+        <v>229</v>
+      </c>
+      <c r="C218">
+        <v>34</v>
+      </c>
+      <c r="D218" t="s">
+        <v>416</v>
+      </c>
+      <c r="E218" t="s">
+        <v>523</v>
+      </c>
+      <c r="F218">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B219" s="1">
+        <v>230</v>
+      </c>
+      <c r="C219">
+        <v>36</v>
+      </c>
+      <c r="D219" t="s">
+        <v>210</v>
+      </c>
+      <c r="E219" t="s">
+        <v>524</v>
+      </c>
+      <c r="F219">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B220" s="1">
+        <v>231</v>
+      </c>
+      <c r="C220">
+        <v>11</v>
+      </c>
+      <c r="D220" t="s">
+        <v>417</v>
+      </c>
+      <c r="E220" t="s">
+        <v>525</v>
+      </c>
+      <c r="F220">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B221" s="1">
+        <v>232</v>
+      </c>
+      <c r="C221">
+        <v>11</v>
+      </c>
+      <c r="D221" t="s">
+        <v>418</v>
+      </c>
+      <c r="E221" t="s">
+        <v>526</v>
+      </c>
+      <c r="F221">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B222" s="1">
+        <v>233</v>
+      </c>
+      <c r="C222">
+        <v>11</v>
+      </c>
+      <c r="D222" t="s">
+        <v>419</v>
+      </c>
+      <c r="E222" t="s">
+        <v>527</v>
+      </c>
+      <c r="F222">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B223" s="1">
+        <v>234</v>
+      </c>
+      <c r="C223">
+        <v>13</v>
+      </c>
+      <c r="D223" t="s">
+        <v>420</v>
+      </c>
+      <c r="E223" t="s">
+        <v>528</v>
+      </c>
+      <c r="F223">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B224" s="1">
+        <v>235</v>
+      </c>
+      <c r="C224">
+        <v>13</v>
+      </c>
+      <c r="D224" t="s">
+        <v>421</v>
+      </c>
+      <c r="E224" t="s">
+        <v>529</v>
+      </c>
+      <c r="F224">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B225" s="1">
+        <v>236</v>
+      </c>
+      <c r="C225">
+        <v>32</v>
+      </c>
+      <c r="D225" t="s">
+        <v>422</v>
+      </c>
+      <c r="E225" t="s">
+        <v>530</v>
+      </c>
+      <c r="F225">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B226" s="1">
+        <v>237</v>
+      </c>
+      <c r="C226">
+        <v>34</v>
+      </c>
+      <c r="D226" t="s">
+        <v>423</v>
+      </c>
+      <c r="E226" t="s">
+        <v>531</v>
+      </c>
+      <c r="F226">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B227" s="1">
+        <v>238</v>
+      </c>
+      <c r="C227">
+        <v>13</v>
+      </c>
+      <c r="D227" t="s">
+        <v>424</v>
+      </c>
+      <c r="E227" t="s">
+        <v>532</v>
+      </c>
+      <c r="F227">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B228" s="1">
+        <v>239</v>
+      </c>
+      <c r="C228">
+        <v>13</v>
+      </c>
+      <c r="D228" t="s">
+        <v>425</v>
+      </c>
+      <c r="E228" t="s">
+        <v>533</v>
+      </c>
+      <c r="F228">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B229" s="1">
+        <v>240</v>
+      </c>
+      <c r="C229">
+        <v>13</v>
+      </c>
+      <c r="D229" t="s">
+        <v>426</v>
+      </c>
+      <c r="E229" t="s">
+        <v>534</v>
+      </c>
+      <c r="F229">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B230" s="1">
+        <v>241</v>
+      </c>
+      <c r="C230">
+        <v>13</v>
+      </c>
+      <c r="D230" t="s">
+        <v>427</v>
+      </c>
+      <c r="E230" t="s">
+        <v>535</v>
+      </c>
+      <c r="F230">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B231" s="1">
+        <v>242</v>
+      </c>
+      <c r="C231">
+        <v>13</v>
+      </c>
+      <c r="D231" t="s">
+        <v>428</v>
+      </c>
+      <c r="E231" t="s">
+        <v>536</v>
+      </c>
+      <c r="F231">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B232" s="1">
+        <v>243</v>
+      </c>
+      <c r="C232">
+        <v>29</v>
+      </c>
+      <c r="D232" t="s">
+        <v>429</v>
+      </c>
+      <c r="E232" t="s">
+        <v>537</v>
+      </c>
+      <c r="F232">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B233" s="1">
+        <v>244</v>
+      </c>
+      <c r="C233">
+        <v>29</v>
+      </c>
+      <c r="D233" t="s">
+        <v>430</v>
+      </c>
+      <c r="E233" t="s">
+        <v>538</v>
+      </c>
+      <c r="F233">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B234" s="1">
+        <v>245</v>
+      </c>
+      <c r="C234">
+        <v>29</v>
+      </c>
+      <c r="D234" t="s">
+        <v>431</v>
+      </c>
+      <c r="E234" t="s">
+        <v>539</v>
+      </c>
+      <c r="F234">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B235" s="1">
+        <v>246</v>
+      </c>
+      <c r="C235">
+        <v>67</v>
+      </c>
+      <c r="D235" t="s">
+        <v>432</v>
+      </c>
+      <c r="E235" t="s">
+        <v>540</v>
+      </c>
+      <c r="F235">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B236" s="1">
+        <v>247</v>
+      </c>
+      <c r="C236">
+        <v>29</v>
+      </c>
+      <c r="D236" t="s">
+        <v>409</v>
+      </c>
+      <c r="E236" t="s">
+        <v>541</v>
+      </c>
+      <c r="F236">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B237" s="1">
+        <v>248</v>
+      </c>
+      <c r="C237">
+        <v>29</v>
+      </c>
+      <c r="D237" t="s">
+        <v>433</v>
+      </c>
+      <c r="E237" t="s">
+        <v>542</v>
+      </c>
+      <c r="F237">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B238" s="1">
+        <v>249</v>
+      </c>
+      <c r="C238">
+        <v>29</v>
+      </c>
+      <c r="D238" t="s">
+        <v>434</v>
+      </c>
+      <c r="E238" t="s">
+        <v>543</v>
+      </c>
+      <c r="F238">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B239" s="1">
+        <v>250</v>
+      </c>
+      <c r="C239">
+        <v>63</v>
+      </c>
+      <c r="D239" t="s">
+        <v>435</v>
+      </c>
+      <c r="E239" t="s">
+        <v>544</v>
+      </c>
+      <c r="F239">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B240" s="1">
+        <v>251</v>
+      </c>
+      <c r="C240">
+        <v>29</v>
+      </c>
+      <c r="D240" t="s">
+        <v>436</v>
+      </c>
+      <c r="E240" t="s">
+        <v>545</v>
+      </c>
+      <c r="F240">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B241" s="1">
+        <v>252</v>
+      </c>
+      <c r="C241">
+        <v>29</v>
+      </c>
+      <c r="D241" t="s">
+        <v>437</v>
+      </c>
+      <c r="E241" t="s">
+        <v>546</v>
+      </c>
+      <c r="F241">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B242" s="1">
+        <v>253</v>
+      </c>
+      <c r="C242">
+        <v>67</v>
+      </c>
+      <c r="D242" t="s">
+        <v>438</v>
+      </c>
+      <c r="E242" t="s">
+        <v>547</v>
+      </c>
+      <c r="F242">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B243" s="1">
+        <v>254</v>
+      </c>
+      <c r="C243">
+        <v>29</v>
+      </c>
+      <c r="D243" t="s">
+        <v>439</v>
+      </c>
+      <c r="E243" t="s">
+        <v>548</v>
+      </c>
+      <c r="F243">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B244" s="1">
+        <v>255</v>
+      </c>
+      <c r="C244">
+        <v>11</v>
+      </c>
+      <c r="D244" t="s">
+        <v>440</v>
+      </c>
+      <c r="E244" t="s">
+        <v>549</v>
+      </c>
+      <c r="F244">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B245" s="1">
+        <v>256</v>
+      </c>
+      <c r="C245">
+        <v>29</v>
+      </c>
+      <c r="D245" t="s">
+        <v>441</v>
+      </c>
+      <c r="E245" t="s">
+        <v>550</v>
+      </c>
+      <c r="F245">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B246" s="1">
+        <v>257</v>
+      </c>
+      <c r="C246">
+        <v>29</v>
+      </c>
+      <c r="D246" t="s">
+        <v>442</v>
+      </c>
+      <c r="E246" t="s">
+        <v>442</v>
+      </c>
+      <c r="F246">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B247" s="1">
+        <v>258</v>
+      </c>
+      <c r="C247">
+        <v>29</v>
+      </c>
+      <c r="D247" t="s">
+        <v>443</v>
+      </c>
+      <c r="E247" t="s">
+        <v>551</v>
+      </c>
+      <c r="F247">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B248" s="1">
+        <v>259</v>
+      </c>
+      <c r="C248">
+        <v>8</v>
+      </c>
+      <c r="D248" t="s">
+        <v>152</v>
+      </c>
+      <c r="E248" t="s">
+        <v>153</v>
+      </c>
+      <c r="F248">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B249" s="1">
+        <v>260</v>
+      </c>
+      <c r="C249">
+        <v>29</v>
+      </c>
+      <c r="D249" t="s">
+        <v>444</v>
+      </c>
+      <c r="E249" t="s">
+        <v>552</v>
+      </c>
+      <c r="F249">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B250" s="1">
+        <v>261</v>
+      </c>
+      <c r="C250">
+        <v>34</v>
+      </c>
+      <c r="D250" t="s">
+        <v>445</v>
+      </c>
+      <c r="E250" t="s">
+        <v>553</v>
+      </c>
+      <c r="F250">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B251" s="1">
+        <v>262</v>
+      </c>
+      <c r="C251">
+        <v>54</v>
+      </c>
+      <c r="D251" t="s">
+        <v>446</v>
+      </c>
+      <c r="E251" t="s">
+        <v>554</v>
+      </c>
+      <c r="F251">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B252" s="1">
+        <v>263</v>
+      </c>
+      <c r="C252">
+        <v>62</v>
+      </c>
+      <c r="D252" t="s">
+        <v>447</v>
+      </c>
+      <c r="E252" t="s">
+        <v>555</v>
+      </c>
+      <c r="F252">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B253" s="1">
+        <v>264</v>
+      </c>
+      <c r="C253">
+        <v>34</v>
+      </c>
+      <c r="D253" t="s">
+        <v>448</v>
+      </c>
+      <c r="E253" t="s">
+        <v>556</v>
+      </c>
+      <c r="F253">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B254" s="1">
+        <v>265</v>
+      </c>
+      <c r="C254">
+        <v>34</v>
+      </c>
+      <c r="D254" t="s">
+        <v>449</v>
+      </c>
+      <c r="E254" t="s">
+        <v>557</v>
+      </c>
+      <c r="F254">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B255" s="1">
+        <v>266</v>
+      </c>
+      <c r="C255">
+        <v>54</v>
+      </c>
+      <c r="D255" t="s">
+        <v>450</v>
+      </c>
+      <c r="E255" t="s">
+        <v>558</v>
+      </c>
+      <c r="F255">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B256" s="1">
+        <v>267</v>
+      </c>
+      <c r="C256">
+        <v>57</v>
+      </c>
+      <c r="D256" t="s">
+        <v>451</v>
+      </c>
+      <c r="E256" t="s">
+        <v>559</v>
+      </c>
+      <c r="F256">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B257" s="1">
+        <v>268</v>
+      </c>
+      <c r="C257">
+        <v>54</v>
+      </c>
+      <c r="D257" t="s">
+        <v>452</v>
+      </c>
+      <c r="E257" t="s">
+        <v>560</v>
+      </c>
+      <c r="F257">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B258" s="1">
+        <v>269</v>
+      </c>
+      <c r="C258">
+        <v>9</v>
+      </c>
+      <c r="D258" t="s">
+        <v>453</v>
+      </c>
+      <c r="E258" t="s">
+        <v>561</v>
+      </c>
+      <c r="F258">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B259" s="1">
+        <v>270</v>
+      </c>
+      <c r="C259">
+        <v>34</v>
+      </c>
+      <c r="D259" t="s">
+        <v>454</v>
+      </c>
+      <c r="E259" t="s">
+        <v>562</v>
+      </c>
+      <c r="F259">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B260" s="1">
+        <v>271</v>
+      </c>
+      <c r="C260">
+        <v>15</v>
+      </c>
+      <c r="D260" t="s">
+        <v>455</v>
+      </c>
+      <c r="E260" t="s">
+        <v>563</v>
+      </c>
+      <c r="F260">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B261" s="1">
+        <v>272</v>
+      </c>
+      <c r="C261">
+        <v>9</v>
+      </c>
+      <c r="D261" t="s">
+        <v>456</v>
+      </c>
+      <c r="E261" t="s">
+        <v>564</v>
+      </c>
+      <c r="F261">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B262" s="1">
+        <v>273</v>
+      </c>
+      <c r="C262">
+        <v>54</v>
+      </c>
+      <c r="D262" t="s">
+        <v>457</v>
+      </c>
+      <c r="E262" t="s">
+        <v>565</v>
+      </c>
+      <c r="F262">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B263" s="1">
+        <v>274</v>
+      </c>
+      <c r="C263">
+        <v>54</v>
+      </c>
+      <c r="D263" t="s">
+        <v>458</v>
+      </c>
+      <c r="E263" t="s">
+        <v>566</v>
+      </c>
+      <c r="F263">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B264" s="1">
+        <v>275</v>
+      </c>
+      <c r="C264">
+        <v>61</v>
+      </c>
+      <c r="D264" t="s">
+        <v>459</v>
+      </c>
+      <c r="E264" t="s">
+        <v>567</v>
+      </c>
+      <c r="F264">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B265" s="1">
+        <v>276</v>
+      </c>
+      <c r="C265">
+        <v>3</v>
+      </c>
+      <c r="D265" t="s">
+        <v>381</v>
+      </c>
+      <c r="E265" t="s">
+        <v>568</v>
+      </c>
+      <c r="F265">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B266" s="1">
+        <v>277</v>
+      </c>
+      <c r="C266">
+        <v>34</v>
+      </c>
+      <c r="D266" t="s">
+        <v>460</v>
+      </c>
+      <c r="E266" t="s">
+        <v>569</v>
+      </c>
+      <c r="F266">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B267" s="1">
+        <v>278</v>
+      </c>
+      <c r="C267">
+        <v>70</v>
+      </c>
+      <c r="D267" t="s">
+        <v>461</v>
+      </c>
+      <c r="E267" t="s">
+        <v>570</v>
+      </c>
+      <c r="F267">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B268" s="1">
+        <v>279</v>
+      </c>
+      <c r="C268">
+        <v>29</v>
+      </c>
+      <c r="D268" t="s">
+        <v>462</v>
+      </c>
+      <c r="E268" t="s">
+        <v>571</v>
+      </c>
+      <c r="F268">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B269" s="1">
+        <v>280</v>
+      </c>
+      <c r="C269">
+        <v>13</v>
+      </c>
+      <c r="D269" t="s">
+        <v>463</v>
+      </c>
+      <c r="E269" t="s">
+        <v>572</v>
+      </c>
+      <c r="F269">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B270" s="1">
+        <v>281</v>
+      </c>
+      <c r="C270">
+        <v>13</v>
+      </c>
+      <c r="D270" t="s">
+        <v>464</v>
+      </c>
+      <c r="E270" t="s">
+        <v>573</v>
+      </c>
+      <c r="F270">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B271" s="1">
+        <v>282</v>
+      </c>
+      <c r="C271">
+        <v>13</v>
+      </c>
+      <c r="D271" t="s">
+        <v>465</v>
+      </c>
+      <c r="E271" t="s">
+        <v>574</v>
+      </c>
+      <c r="F271">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B272" s="1">
+        <v>283</v>
+      </c>
+      <c r="C272">
+        <v>13</v>
+      </c>
+      <c r="D272" t="s">
+        <v>466</v>
+      </c>
+      <c r="E272" t="s">
+        <v>575</v>
+      </c>
+      <c r="F272">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B273" s="1">
+        <v>284</v>
+      </c>
+      <c r="C273">
+        <v>13</v>
+      </c>
+      <c r="D273" t="s">
+        <v>467</v>
+      </c>
+      <c r="E273" t="s">
+        <v>576</v>
+      </c>
+      <c r="F273">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B274" s="1">
+        <v>285</v>
+      </c>
+      <c r="C274">
+        <v>13</v>
+      </c>
+      <c r="D274" t="s">
+        <v>468</v>
+      </c>
+      <c r="E274" t="s">
+        <v>577</v>
+      </c>
+      <c r="F274">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B275" s="1">
+        <v>286</v>
+      </c>
+      <c r="C275">
+        <v>13</v>
+      </c>
+      <c r="D275" t="s">
+        <v>469</v>
+      </c>
+      <c r="E275" t="s">
+        <v>578</v>
+      </c>
+      <c r="F275">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B276" s="1">
+        <v>287</v>
+      </c>
+      <c r="C276">
+        <v>13</v>
+      </c>
+      <c r="D276" t="s">
+        <v>470</v>
+      </c>
+      <c r="E276" t="s">
+        <v>579</v>
+      </c>
+      <c r="F276">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B277" s="1">
+        <v>288</v>
+      </c>
+      <c r="C277">
+        <v>13</v>
+      </c>
+      <c r="D277" t="s">
+        <v>106</v>
+      </c>
+      <c r="E277" t="s">
+        <v>580</v>
+      </c>
+      <c r="F277">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B278" s="1">
+        <v>289</v>
+      </c>
+      <c r="C278">
+        <v>13</v>
+      </c>
+      <c r="D278" t="s">
+        <v>471</v>
+      </c>
+      <c r="E278" t="s">
+        <v>581</v>
+      </c>
+      <c r="F278">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B279" s="1">
+        <v>290</v>
+      </c>
+      <c r="C279">
+        <v>32</v>
+      </c>
+      <c r="D279" t="s">
+        <v>472</v>
+      </c>
+      <c r="E279" t="s">
+        <v>582</v>
+      </c>
+      <c r="F279">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B280" s="1">
+        <v>291</v>
+      </c>
+      <c r="C280">
+        <v>66</v>
+      </c>
+      <c r="D280" t="s">
+        <v>473</v>
+      </c>
+      <c r="E280" t="s">
+        <v>583</v>
+      </c>
+      <c r="F280">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B281" s="1">
+        <v>292</v>
+      </c>
+      <c r="C281">
+        <v>66</v>
+      </c>
+      <c r="D281" t="s">
+        <v>474</v>
+      </c>
+      <c r="E281" t="s">
+        <v>584</v>
+      </c>
+      <c r="F281">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B282" s="1">
+        <v>293</v>
+      </c>
+      <c r="C282">
+        <v>20</v>
+      </c>
+      <c r="D282" t="s">
+        <v>475</v>
+      </c>
+      <c r="E282" t="s">
+        <v>585</v>
+      </c>
+      <c r="F282">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B283" s="1">
+        <v>294</v>
+      </c>
+      <c r="C283">
+        <v>20</v>
+      </c>
+      <c r="D283" t="s">
+        <v>476</v>
+      </c>
+      <c r="E283" t="s">
+        <v>586</v>
+      </c>
+      <c r="F283">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B284" s="1">
+        <v>295</v>
+      </c>
+      <c r="C284">
+        <v>20</v>
+      </c>
+      <c r="D284" t="s">
+        <v>477</v>
+      </c>
+      <c r="E284" t="s">
+        <v>587</v>
+      </c>
+      <c r="F284">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B285" s="1">
+        <v>296</v>
+      </c>
+      <c r="C285">
+        <v>20</v>
+      </c>
+      <c r="D285" t="s">
+        <v>478</v>
+      </c>
+      <c r="E285" t="s">
+        <v>588</v>
+      </c>
+      <c r="F285">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B286" s="1">
+        <v>297</v>
+      </c>
+      <c r="C286">
+        <v>20</v>
+      </c>
+      <c r="D286" t="s">
+        <v>479</v>
+      </c>
+      <c r="E286" t="s">
+        <v>589</v>
+      </c>
+      <c r="F286">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B287" s="1">
+        <v>298</v>
+      </c>
+      <c r="C287">
+        <v>20</v>
+      </c>
+      <c r="D287" t="s">
+        <v>480</v>
+      </c>
+      <c r="E287" t="s">
+        <v>590</v>
+      </c>
+      <c r="F287">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B288" s="1">
+        <v>299</v>
+      </c>
+      <c r="C288">
+        <v>20</v>
+      </c>
+      <c r="D288" t="s">
+        <v>390</v>
+      </c>
+      <c r="E288" t="s">
+        <v>591</v>
+      </c>
+      <c r="F288">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B289" s="1">
+        <v>300</v>
+      </c>
+      <c r="C289">
+        <v>63</v>
+      </c>
+      <c r="D289" t="s">
+        <v>481</v>
+      </c>
+      <c r="E289" t="s">
+        <v>592</v>
+      </c>
+      <c r="F289">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B290" s="1">
+        <v>301</v>
+      </c>
+      <c r="C290">
+        <v>29</v>
+      </c>
+      <c r="D290" t="s">
+        <v>482</v>
+      </c>
+      <c r="E290" t="s">
+        <v>593</v>
+      </c>
+      <c r="F290">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B291" s="1">
+        <v>302</v>
+      </c>
+      <c r="C291">
+        <v>29</v>
+      </c>
+      <c r="D291" t="s">
+        <v>162</v>
+      </c>
+      <c r="E291" t="s">
+        <v>163</v>
+      </c>
+      <c r="F291">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B292" s="1">
+        <v>303</v>
+      </c>
+      <c r="C292">
+        <v>29</v>
+      </c>
+      <c r="D292" t="s">
+        <v>483</v>
+      </c>
+      <c r="E292" t="s">
+        <v>483</v>
+      </c>
+      <c r="F292">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B293" s="1">
+        <v>304</v>
+      </c>
+      <c r="C293">
+        <v>29</v>
+      </c>
+      <c r="D293" t="s">
+        <v>484</v>
+      </c>
+      <c r="E293" t="s">
+        <v>594</v>
+      </c>
+      <c r="F293">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B294" s="1">
+        <v>305</v>
+      </c>
+      <c r="C294">
+        <v>34</v>
+      </c>
+      <c r="D294" t="s">
+        <v>485</v>
+      </c>
+      <c r="E294" t="s">
+        <v>595</v>
+      </c>
+      <c r="F294">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B295" s="1">
+        <v>306</v>
+      </c>
+      <c r="C295">
+        <v>34</v>
+      </c>
+      <c r="D295" t="s">
+        <v>486</v>
+      </c>
+      <c r="E295" t="s">
+        <v>596</v>
+      </c>
+      <c r="F295">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B296" s="1">
+        <v>307</v>
+      </c>
+      <c r="C296">
+        <v>34</v>
+      </c>
+      <c r="D296" t="s">
+        <v>487</v>
+      </c>
+      <c r="E296" t="s">
+        <v>597</v>
+      </c>
+      <c r="F296">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B297" s="1">
+        <v>308</v>
+      </c>
+      <c r="C297">
+        <v>31</v>
+      </c>
+      <c r="D297" t="s">
+        <v>488</v>
+      </c>
+      <c r="E297" t="s">
+        <v>598</v>
+      </c>
+      <c r="F297">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B298" s="1">
+        <v>309</v>
+      </c>
+      <c r="C298">
+        <v>55</v>
+      </c>
+      <c r="D298" t="s">
+        <v>489</v>
+      </c>
+      <c r="E298" t="s">
+        <v>599</v>
+      </c>
+      <c r="F298">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B299" s="1">
+        <v>310</v>
+      </c>
+      <c r="C299">
+        <v>60</v>
+      </c>
+      <c r="D299" t="s">
+        <v>490</v>
+      </c>
+      <c r="E299" t="s">
+        <v>600</v>
+      </c>
+      <c r="F299">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B300" s="1">
+        <v>311</v>
+      </c>
+      <c r="C300">
+        <v>56</v>
+      </c>
+      <c r="D300" t="s">
+        <v>491</v>
+      </c>
+      <c r="E300" t="s">
+        <v>601</v>
+      </c>
+      <c r="F300">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B301" s="1">
+        <v>312</v>
+      </c>
+      <c r="C301">
+        <v>34</v>
+      </c>
+      <c r="D301" t="s">
+        <v>492</v>
+      </c>
+      <c r="E301" t="s">
+        <v>602</v>
+      </c>
+      <c r="F301">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B302" s="1">
+        <v>313</v>
+      </c>
+      <c r="C302">
+        <v>34</v>
+      </c>
+      <c r="D302" t="s">
+        <v>493</v>
+      </c>
+      <c r="E302" t="s">
+        <v>603</v>
+      </c>
+      <c r="F302">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B303" s="1">
+        <v>314</v>
+      </c>
+      <c r="C303">
+        <v>61</v>
+      </c>
+      <c r="D303" t="s">
+        <v>494</v>
+      </c>
+      <c r="E303" t="s">
+        <v>604</v>
+      </c>
+      <c r="F303">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B304" s="1">
+        <v>315</v>
+      </c>
+      <c r="C304">
+        <v>57</v>
+      </c>
+      <c r="D304" t="s">
+        <v>495</v>
+      </c>
+      <c r="E304" t="s">
+        <v>605</v>
+      </c>
+      <c r="F304">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B305" s="1">
+        <v>316</v>
+      </c>
+      <c r="C305">
+        <v>34</v>
+      </c>
+      <c r="D305" t="s">
+        <v>496</v>
+      </c>
+      <c r="E305" t="s">
+        <v>606</v>
+      </c>
+      <c r="F305">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B306" s="1">
+        <v>317</v>
+      </c>
+      <c r="C306">
+        <v>56</v>
+      </c>
+      <c r="D306" t="s">
+        <v>497</v>
+      </c>
+      <c r="E306" t="s">
+        <v>607</v>
+      </c>
+      <c r="F306">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B307" s="1">
+        <v>318</v>
+      </c>
+      <c r="C307">
+        <v>34</v>
+      </c>
+      <c r="D307" t="s">
+        <v>498</v>
+      </c>
+      <c r="E307" t="s">
+        <v>608</v>
+      </c>
+      <c r="F307">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B308" s="1">
+        <v>319</v>
+      </c>
+      <c r="C308">
+        <v>61</v>
+      </c>
+      <c r="D308" t="s">
+        <v>499</v>
+      </c>
+      <c r="E308" t="s">
+        <v>609</v>
+      </c>
+      <c r="F308">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B309" s="1">
+        <v>320</v>
+      </c>
+      <c r="C309">
+        <v>34</v>
+      </c>
+      <c r="D309" t="s">
+        <v>500</v>
+      </c>
+      <c r="E309" t="s">
+        <v>610</v>
+      </c>
+      <c r="F309">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B310" s="1">
+        <v>321</v>
+      </c>
+      <c r="C310">
+        <v>34</v>
+      </c>
+      <c r="D310" t="s">
+        <v>501</v>
+      </c>
+      <c r="E310" t="s">
+        <v>611</v>
+      </c>
+      <c r="F310">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B311" s="1">
+        <v>322</v>
+      </c>
+      <c r="C311">
+        <v>34</v>
+      </c>
+      <c r="D311" t="s">
+        <v>502</v>
+      </c>
+      <c r="E311" t="s">
+        <v>612</v>
+      </c>
+      <c r="F311">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B312" s="1">
+        <v>323</v>
+      </c>
+      <c r="C312">
+        <v>57</v>
+      </c>
+      <c r="D312" t="s">
+        <v>503</v>
+      </c>
+      <c r="E312" t="s">
+        <v>613</v>
+      </c>
+      <c r="F312">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B313" s="1">
+        <v>324</v>
+      </c>
+      <c r="C313">
+        <v>55</v>
+      </c>
+      <c r="D313" t="s">
+        <v>504</v>
+      </c>
+      <c r="E313" t="s">
+        <v>614</v>
+      </c>
+      <c r="F313">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B314" s="1">
+        <v>325</v>
+      </c>
+      <c r="C314">
+        <v>63</v>
+      </c>
+      <c r="D314" t="s">
+        <v>505</v>
+      </c>
+      <c r="E314" t="s">
+        <v>615</v>
+      </c>
+      <c r="F314">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B315" s="1">
+        <v>326</v>
+      </c>
+      <c r="C315">
+        <v>63</v>
+      </c>
+      <c r="D315" t="s">
+        <v>506</v>
+      </c>
+      <c r="E315" t="s">
+        <v>616</v>
+      </c>
+      <c r="F315">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B316" s="1">
+        <v>327</v>
+      </c>
+      <c r="C316">
+        <v>20</v>
+      </c>
+      <c r="D316" t="s">
+        <v>507</v>
+      </c>
+      <c r="E316" t="s">
+        <v>617</v>
+      </c>
+      <c r="F316">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B317" s="1">
+        <v>328</v>
+      </c>
+      <c r="C317">
+        <v>55</v>
+      </c>
+      <c r="D317" t="s">
+        <v>449</v>
+      </c>
+      <c r="E317" t="s">
+        <v>557</v>
+      </c>
+      <c r="F317">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B318" s="1">
+        <v>329</v>
+      </c>
+      <c r="C318">
+        <v>55</v>
+      </c>
+      <c r="D318" t="s">
+        <v>508</v>
+      </c>
+      <c r="E318" t="s">
+        <v>618</v>
+      </c>
+      <c r="F318">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B319" s="1">
+        <v>330</v>
+      </c>
+      <c r="C319">
+        <v>20</v>
+      </c>
+      <c r="D319" t="s">
+        <v>509</v>
+      </c>
+      <c r="E319" t="s">
+        <v>619</v>
+      </c>
+      <c r="F319">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B320" s="1">
+        <v>331</v>
+      </c>
+      <c r="C320">
+        <v>66</v>
+      </c>
+      <c r="D320" t="s">
+        <v>510</v>
+      </c>
+      <c r="E320" t="s">
+        <v>620</v>
+      </c>
+      <c r="F320">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B321" s="1">
+        <v>332</v>
+      </c>
+      <c r="C321">
+        <v>64</v>
+      </c>
+      <c r="D321" t="s">
+        <v>511</v>
+      </c>
+      <c r="E321" t="s">
+        <v>621</v>
+      </c>
+      <c r="F321">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B322" s="1">
+        <v>333</v>
+      </c>
+      <c r="C322">
+        <v>68</v>
+      </c>
+      <c r="D322" t="s">
+        <v>512</v>
+      </c>
+      <c r="E322" t="s">
+        <v>622</v>
+      </c>
+      <c r="F322">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/db/data/office_items.xlsx
+++ b/db/data/office_items.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\storemgmt\db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1499A608-33F4-4C7A-93B4-A9298D88A21C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,18 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="616">
   <si>
     <t>temp_id</t>
   </si>
@@ -236,12 +231,6 @@
     <t>बैज्ञानिक क्यालकुलेटर</t>
   </si>
   <si>
-    <t>Voltage Guard</t>
-  </si>
-  <si>
-    <t>भोल्टेज गार्ड</t>
-  </si>
-  <si>
     <t>Usha ceiling fan</t>
   </si>
   <si>
@@ -506,12 +495,6 @@
     <t>साधारण स्टिल डिस</t>
   </si>
   <si>
-    <t>Computer Chesis 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">कम्प्युटर चेसिस ३ </t>
-  </si>
-  <si>
     <t>Monitor</t>
   </si>
   <si>
@@ -839,12 +822,6 @@
     <t>पानी परिक्षण किट (चार्जर सहित)</t>
   </si>
   <si>
-    <t>Mechanical Jack</t>
-  </si>
-  <si>
-    <t>मेकानिकल ज्याक मेशिन</t>
-  </si>
-  <si>
     <t>110x140mm Clamp</t>
   </si>
   <si>
@@ -980,12 +957,6 @@
     <t>चरेसको कटौरा</t>
   </si>
   <si>
-    <t>Dell Laptop</t>
-  </si>
-  <si>
-    <t>डेल ल्यापटप</t>
-  </si>
-  <si>
     <t>HO Maruti Chair</t>
   </si>
   <si>
@@ -1046,9 +1017,6 @@
     <t>खुकुरी सोफा</t>
   </si>
   <si>
-    <t xml:space="preserve">Dell Laptop </t>
-  </si>
-  <si>
     <t>Tea Table Nagin Bath leg</t>
   </si>
   <si>
@@ -1899,12 +1867,18 @@
   </si>
   <si>
     <t>सर्भे रिपोर्ट</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>ल्यापटप</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2257,8 +2231,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F322"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F318"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2270,7 +2244,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2285,7 +2259,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2772,10 +2746,10 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E30" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F30">
         <v>47</v>
@@ -2851,10 +2825,10 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>68</v>
@@ -2868,10 +2842,10 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -2885,10 +2859,10 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
         <v>72</v>
@@ -2902,10 +2876,10 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
         <v>74</v>
@@ -2919,10 +2893,10 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
         <v>76</v>
@@ -2936,7 +2910,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C40">
         <v>19</v>
@@ -2953,10 +2927,10 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
         <v>80</v>
@@ -2970,10 +2944,10 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C42">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
         <v>82</v>
@@ -2987,10 +2961,10 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
         <v>84</v>
@@ -3004,10 +2978,10 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" t="s">
         <v>86</v>
@@ -3021,10 +2995,10 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="s">
         <v>88</v>
@@ -3038,7 +3012,7 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3055,10 +3029,10 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
         <v>92</v>
@@ -3072,10 +3046,10 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="s">
         <v>94</v>
@@ -3089,10 +3063,10 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
         <v>96</v>
@@ -3106,10 +3080,10 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
         <v>98</v>
@@ -3123,7 +3097,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C51">
         <v>18</v>
@@ -3140,10 +3114,10 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C52">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
         <v>102</v>
@@ -3157,7 +3131,7 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53">
         <v>13</v>
@@ -3174,16 +3148,16 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54">
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="F54">
         <v>47</v>
@@ -3191,16 +3165,16 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55">
         <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="F55">
         <v>47</v>
@@ -3208,7 +3182,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56">
         <v>13</v>
@@ -3225,7 +3199,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C57">
         <v>13</v>
@@ -3242,7 +3216,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C58">
         <v>13</v>
@@ -3259,7 +3233,7 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C59">
         <v>13</v>
@@ -3276,10 +3250,10 @@
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C60">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D60" t="s">
         <v>116</v>
@@ -3293,10 +3267,10 @@
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D61" t="s">
         <v>118</v>
@@ -3310,10 +3284,10 @@
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
         <v>120</v>
@@ -3327,10 +3301,10 @@
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="s">
         <v>122</v>
@@ -3344,10 +3318,10 @@
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
         <v>124</v>
@@ -3361,10 +3335,10 @@
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C65">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
         <v>126</v>
@@ -3378,10 +3352,10 @@
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>128</v>
@@ -3395,10 +3369,10 @@
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C67">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
         <v>130</v>
@@ -3412,10 +3386,10 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C68">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D68" t="s">
         <v>132</v>
@@ -3429,10 +3403,10 @@
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C69">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
@@ -3446,10 +3420,10 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C70">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
         <v>136</v>
@@ -3463,10 +3437,10 @@
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D71" t="s">
         <v>138</v>
@@ -3480,10 +3454,10 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
         <v>140</v>
@@ -3497,10 +3471,10 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C73">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D73" t="s">
         <v>142</v>
@@ -3514,7 +3488,7 @@
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>25</v>
@@ -3531,10 +3505,10 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C75">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
         <v>146</v>
@@ -3548,10 +3522,10 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
         <v>148</v>
@@ -3565,10 +3539,10 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
         <v>150</v>
@@ -3582,10 +3556,10 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C78">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
         <v>152</v>
@@ -3599,7 +3573,7 @@
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79">
         <v>13</v>
@@ -3616,10 +3590,10 @@
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C80">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D80" t="s">
         <v>156</v>
@@ -3633,7 +3607,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C81">
         <v>29</v>
@@ -3650,10 +3624,10 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C82">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D82" t="s">
         <v>160</v>
@@ -3667,7 +3641,7 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C83">
         <v>29</v>
@@ -3684,10 +3658,10 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D84" t="s">
         <v>164</v>
@@ -3701,10 +3675,10 @@
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C85">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D85" t="s">
         <v>166</v>
@@ -3718,10 +3692,10 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D86" t="s">
         <v>168</v>
@@ -3735,10 +3709,10 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C87">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D87" t="s">
         <v>170</v>
@@ -3752,10 +3726,10 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s">
         <v>172</v>
@@ -3769,10 +3743,10 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C89">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D89" t="s">
         <v>174</v>
@@ -3786,10 +3760,10 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C90">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D90" t="s">
         <v>176</v>
@@ -3803,7 +3777,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -3820,10 +3794,10 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D92" t="s">
         <v>180</v>
@@ -3837,10 +3811,10 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D93" t="s">
         <v>182</v>
@@ -3854,10 +3828,10 @@
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D94" t="s">
         <v>184</v>
@@ -3871,16 +3845,16 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C95">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="F95">
         <v>47</v>
@@ -3888,16 +3862,16 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C96">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D96" t="s">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="E96" t="s">
-        <v>189</v>
+        <v>393</v>
       </c>
       <c r="F96">
         <v>47</v>
@@ -3905,16 +3879,16 @@
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C97">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="E97" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="F97">
         <v>47</v>
@@ -3922,16 +3896,16 @@
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C98">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>401</v>
+        <v>188</v>
       </c>
       <c r="E98" t="s">
-        <v>402</v>
+        <v>189</v>
       </c>
       <c r="F98">
         <v>47</v>
@@ -3939,16 +3913,16 @@
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C99">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="E99" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="F99">
         <v>47</v>
@@ -3956,16 +3930,16 @@
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E100" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F100">
         <v>47</v>
@@ -3973,16 +3947,16 @@
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E101" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="F101">
         <v>47</v>
@@ -3990,10 +3964,10 @@
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D102" t="s">
         <v>194</v>
@@ -4007,10 +3981,10 @@
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C103">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D103" t="s">
         <v>196</v>
@@ -4024,10 +3998,10 @@
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C104">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
         <v>198</v>
@@ -4041,10 +4015,10 @@
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C105">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
         <v>200</v>
@@ -4058,10 +4032,10 @@
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D106" t="s">
         <v>202</v>
@@ -4075,10 +4049,10 @@
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C107">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D107" t="s">
         <v>204</v>
@@ -4092,10 +4066,10 @@
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s">
         <v>206</v>
@@ -4109,10 +4083,10 @@
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C109">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D109" t="s">
         <v>208</v>
@@ -4126,10 +4100,10 @@
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C110">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D110" t="s">
         <v>210</v>
@@ -4143,10 +4117,10 @@
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B111">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D111" t="s">
         <v>212</v>
@@ -4160,10 +4134,10 @@
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C112">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
         <v>214</v>
@@ -4177,7 +4151,7 @@
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C113">
         <v>11</v>
@@ -4194,7 +4168,7 @@
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C114">
         <v>11</v>
@@ -4211,10 +4185,10 @@
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C115">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D115" t="s">
         <v>220</v>
@@ -4228,10 +4202,10 @@
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C116">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D116" t="s">
         <v>222</v>
@@ -4245,10 +4219,10 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C117">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D117" t="s">
         <v>224</v>
@@ -4262,16 +4236,16 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C118">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
+        <v>150</v>
+      </c>
+      <c r="E118" t="s">
         <v>226</v>
-      </c>
-      <c r="E118" t="s">
-        <v>227</v>
       </c>
       <c r="F118">
         <v>47</v>
@@ -4279,16 +4253,16 @@
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C119">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D119" t="s">
+        <v>227</v>
+      </c>
+      <c r="E119" t="s">
         <v>228</v>
-      </c>
-      <c r="E119" t="s">
-        <v>229</v>
       </c>
       <c r="F119">
         <v>47</v>
@@ -4296,13 +4270,13 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="E120" t="s">
         <v>230</v>
@@ -4313,10 +4287,10 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C121">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D121" t="s">
         <v>231</v>
@@ -4330,10 +4304,10 @@
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C122">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D122" t="s">
         <v>233</v>
@@ -4347,10 +4321,10 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C123">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D123" t="s">
         <v>235</v>
@@ -4364,10 +4338,10 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C124">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
         <v>237</v>
@@ -4381,10 +4355,10 @@
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C125">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D125" t="s">
         <v>239</v>
@@ -4398,10 +4372,10 @@
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C126">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D126" t="s">
         <v>241</v>
@@ -4415,10 +4389,10 @@
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C127">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D127" t="s">
         <v>243</v>
@@ -4432,10 +4406,10 @@
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C128">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
         <v>245</v>
@@ -4449,10 +4423,10 @@
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C129">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D129" t="s">
         <v>247</v>
@@ -4466,10 +4440,10 @@
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D130" t="s">
         <v>249</v>
@@ -4483,10 +4457,10 @@
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C131">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D131" t="s">
         <v>251</v>
@@ -4500,10 +4474,10 @@
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C132">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D132" t="s">
         <v>253</v>
@@ -4517,10 +4491,10 @@
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" t="s">
         <v>255</v>
@@ -4534,10 +4508,10 @@
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D134" t="s">
         <v>257</v>
@@ -4551,10 +4525,10 @@
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" t="s">
         <v>259</v>
@@ -4568,10 +4542,10 @@
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C136">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s">
         <v>261</v>
@@ -4585,10 +4559,10 @@
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C137">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D137" t="s">
         <v>263</v>
@@ -4602,10 +4576,10 @@
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C138">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D138" t="s">
         <v>265</v>
@@ -4619,10 +4593,10 @@
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C139">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
         <v>267</v>
@@ -4636,10 +4610,10 @@
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C140">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D140" t="s">
         <v>269</v>
@@ -4653,10 +4627,10 @@
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C141">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D141" t="s">
         <v>271</v>
@@ -4670,10 +4644,10 @@
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C142">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D142" t="s">
         <v>273</v>
@@ -4687,10 +4661,10 @@
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C143">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D143" t="s">
         <v>275</v>
@@ -4704,10 +4678,10 @@
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C144">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D144" t="s">
         <v>277</v>
@@ -4721,10 +4695,10 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B145">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C145">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D145" t="s">
         <v>279</v>
@@ -4738,10 +4712,10 @@
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B146">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C146">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D146" t="s">
         <v>281</v>
@@ -4755,10 +4729,10 @@
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B147">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C147">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D147" t="s">
         <v>283</v>
@@ -4772,10 +4746,10 @@
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C148">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D148" t="s">
         <v>285</v>
@@ -4789,10 +4763,10 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B149">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C149">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D149" t="s">
         <v>287</v>
@@ -4806,10 +4780,10 @@
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B150">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C150">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D150" t="s">
         <v>289</v>
@@ -4823,10 +4797,10 @@
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C151">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D151" t="s">
         <v>291</v>
@@ -4840,10 +4814,10 @@
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B152">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C152">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D152" t="s">
         <v>293</v>
@@ -4857,10 +4831,10 @@
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B153">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C153">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D153" t="s">
         <v>295</v>
@@ -4874,7 +4848,7 @@
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B154">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C154">
         <v>34</v>
@@ -4891,10 +4865,10 @@
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B155">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C155">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D155" t="s">
         <v>299</v>
@@ -4908,10 +4882,10 @@
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C156">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D156" t="s">
         <v>301</v>
@@ -4925,16 +4899,16 @@
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B157">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C157">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D157" t="s">
+        <v>239</v>
+      </c>
+      <c r="E157" t="s">
         <v>303</v>
-      </c>
-      <c r="E157" t="s">
-        <v>304</v>
       </c>
       <c r="F157">
         <v>47</v>
@@ -4942,16 +4916,16 @@
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C158">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D158" t="s">
+        <v>304</v>
+      </c>
+      <c r="E158" t="s">
         <v>305</v>
-      </c>
-      <c r="E158" t="s">
-        <v>306</v>
       </c>
       <c r="F158">
         <v>47</v>
@@ -4959,16 +4933,16 @@
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B159">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C159">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D159" t="s">
+        <v>306</v>
+      </c>
+      <c r="E159" t="s">
         <v>307</v>
-      </c>
-      <c r="E159" t="s">
-        <v>308</v>
       </c>
       <c r="F159">
         <v>47</v>
@@ -4976,13 +4950,13 @@
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B160">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C160">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D160" t="s">
-        <v>243</v>
+        <v>308</v>
       </c>
       <c r="E160" t="s">
         <v>309</v>
@@ -4993,16 +4967,16 @@
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C161">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D161" t="s">
-        <v>310</v>
+        <v>614</v>
       </c>
       <c r="E161" t="s">
-        <v>311</v>
+        <v>615</v>
       </c>
       <c r="F161">
         <v>47</v>
@@ -5010,16 +4984,16 @@
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C162">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E162" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F162">
         <v>47</v>
@@ -5027,16 +5001,16 @@
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C163">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="D163" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E163" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F163">
         <v>47</v>
@@ -5044,16 +5018,16 @@
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C164">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D164" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E164" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F164">
         <v>47</v>
@@ -5061,16 +5035,16 @@
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C165">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D165" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E165" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F165">
         <v>47</v>
@@ -5078,16 +5052,16 @@
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C166">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D166" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E166" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F166">
         <v>47</v>
@@ -5095,16 +5069,16 @@
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C167">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D167" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E167" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F167">
         <v>47</v>
@@ -5112,16 +5086,16 @@
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C168">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E168" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F168">
         <v>47</v>
@@ -5129,16 +5103,16 @@
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C169">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D169" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E169" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F169">
         <v>47</v>
@@ -5146,16 +5120,16 @@
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C170">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D170" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E170" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F170">
         <v>47</v>
@@ -5163,16 +5137,16 @@
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C171">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D171" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E171" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F171">
         <v>47</v>
@@ -5180,16 +5154,16 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D172" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E172" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F172">
         <v>47</v>
@@ -5197,16 +5171,16 @@
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C173">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D173" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E173" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F173">
         <v>47</v>
@@ -5214,16 +5188,16 @@
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C174">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D174" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E174" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F174">
         <v>47</v>
@@ -5231,16 +5205,16 @@
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C175">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D175" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E175" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="F175">
         <v>47</v>
@@ -5248,16 +5222,16 @@
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C176">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D176" t="s">
+        <v>338</v>
+      </c>
+      <c r="E176" t="s">
         <v>339</v>
-      </c>
-      <c r="E176" t="s">
-        <v>340</v>
       </c>
       <c r="F176">
         <v>47</v>
@@ -5265,16 +5239,16 @@
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D177" t="s">
+        <v>340</v>
+      </c>
+      <c r="E177" t="s">
         <v>341</v>
-      </c>
-      <c r="E177" t="s">
-        <v>342</v>
       </c>
       <c r="F177">
         <v>47</v>
@@ -5282,16 +5256,16 @@
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C178">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D178" t="s">
+        <v>342</v>
+      </c>
+      <c r="E178" t="s">
         <v>343</v>
-      </c>
-      <c r="E178" t="s">
-        <v>344</v>
       </c>
       <c r="F178">
         <v>47</v>
@@ -5299,16 +5273,16 @@
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C179">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="D179" t="s">
+        <v>344</v>
+      </c>
+      <c r="E179" t="s">
         <v>345</v>
-      </c>
-      <c r="E179" t="s">
-        <v>346</v>
       </c>
       <c r="F179">
         <v>47</v>
@@ -5316,16 +5290,16 @@
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B180">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C180">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D180" t="s">
+        <v>346</v>
+      </c>
+      <c r="E180" t="s">
         <v>347</v>
-      </c>
-      <c r="E180" t="s">
-        <v>348</v>
       </c>
       <c r="F180">
         <v>47</v>
@@ -5333,16 +5307,16 @@
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B181">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C181">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D181" t="s">
+        <v>348</v>
+      </c>
+      <c r="E181" t="s">
         <v>349</v>
-      </c>
-      <c r="E181" t="s">
-        <v>350</v>
       </c>
       <c r="F181">
         <v>47</v>
@@ -5350,16 +5324,16 @@
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C182">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D182" t="s">
+        <v>350</v>
+      </c>
+      <c r="E182" t="s">
         <v>351</v>
-      </c>
-      <c r="E182" t="s">
-        <v>352</v>
       </c>
       <c r="F182">
         <v>47</v>
@@ -5367,16 +5341,16 @@
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C183">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D183" t="s">
+        <v>352</v>
+      </c>
+      <c r="E183" t="s">
         <v>353</v>
-      </c>
-      <c r="E183" t="s">
-        <v>354</v>
       </c>
       <c r="F183">
         <v>47</v>
@@ -5384,16 +5358,16 @@
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C184">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D184" t="s">
+        <v>354</v>
+      </c>
+      <c r="E184" t="s">
         <v>355</v>
-      </c>
-      <c r="E184" t="s">
-        <v>356</v>
       </c>
       <c r="F184">
         <v>47</v>
@@ -5401,16 +5375,16 @@
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B185">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C185">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D185" t="s">
+        <v>356</v>
+      </c>
+      <c r="E185" t="s">
         <v>357</v>
-      </c>
-      <c r="E185" t="s">
-        <v>358</v>
       </c>
       <c r="F185">
         <v>47</v>
@@ -5418,16 +5392,16 @@
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C186">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D186" t="s">
+        <v>358</v>
+      </c>
+      <c r="E186" t="s">
         <v>359</v>
-      </c>
-      <c r="E186" t="s">
-        <v>360</v>
       </c>
       <c r="F186">
         <v>47</v>
@@ -5435,16 +5409,16 @@
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C187">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D187" t="s">
+        <v>360</v>
+      </c>
+      <c r="E187" t="s">
         <v>361</v>
-      </c>
-      <c r="E187" t="s">
-        <v>362</v>
       </c>
       <c r="F187">
         <v>47</v>
@@ -5452,16 +5426,16 @@
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C188">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D188" t="s">
+        <v>362</v>
+      </c>
+      <c r="E188" t="s">
         <v>363</v>
-      </c>
-      <c r="E188" t="s">
-        <v>364</v>
       </c>
       <c r="F188">
         <v>47</v>
@@ -5469,16 +5443,16 @@
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C189">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D189" t="s">
+        <v>364</v>
+      </c>
+      <c r="E189" t="s">
         <v>365</v>
-      </c>
-      <c r="E189" t="s">
-        <v>366</v>
       </c>
       <c r="F189">
         <v>47</v>
@@ -5486,16 +5460,16 @@
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C190">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D190" t="s">
+        <v>366</v>
+      </c>
+      <c r="E190" t="s">
         <v>367</v>
-      </c>
-      <c r="E190" t="s">
-        <v>368</v>
       </c>
       <c r="F190">
         <v>47</v>
@@ -5503,16 +5477,16 @@
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C191">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D191" t="s">
+        <v>368</v>
+      </c>
+      <c r="E191" t="s">
         <v>369</v>
-      </c>
-      <c r="E191" t="s">
-        <v>370</v>
       </c>
       <c r="F191">
         <v>47</v>
@@ -5520,16 +5494,16 @@
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C192">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D192" t="s">
+        <v>370</v>
+      </c>
+      <c r="E192" t="s">
         <v>371</v>
-      </c>
-      <c r="E192" t="s">
-        <v>372</v>
       </c>
       <c r="F192">
         <v>47</v>
@@ -5537,16 +5511,16 @@
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B193">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C193">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D193" t="s">
+        <v>372</v>
+      </c>
+      <c r="E193" t="s">
         <v>373</v>
-      </c>
-      <c r="E193" t="s">
-        <v>374</v>
       </c>
       <c r="F193">
         <v>47</v>
@@ -5554,16 +5528,16 @@
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B194">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C194">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D194" t="s">
+        <v>374</v>
+      </c>
+      <c r="E194" t="s">
         <v>375</v>
-      </c>
-      <c r="E194" t="s">
-        <v>376</v>
       </c>
       <c r="F194">
         <v>47</v>
@@ -5571,16 +5545,16 @@
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C195">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E195" t="s">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="F195">
         <v>47</v>
@@ -5588,16 +5562,16 @@
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C196">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>379</v>
+        <v>184</v>
       </c>
       <c r="E196" t="s">
-        <v>380</v>
+        <v>185</v>
       </c>
       <c r="F196">
         <v>47</v>
@@ -5605,16 +5579,16 @@
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C197">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D197" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E197" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F197">
         <v>47</v>
@@ -5622,16 +5596,16 @@
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C198">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D198" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E198" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F198">
         <v>47</v>
@@ -5639,16 +5613,16 @@
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C199">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D199" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E199" t="s">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="F199">
         <v>47</v>
@@ -5656,16 +5630,16 @@
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C200">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D200" t="s">
-        <v>188</v>
+        <v>383</v>
       </c>
       <c r="E200" t="s">
-        <v>189</v>
+        <v>384</v>
       </c>
       <c r="F200">
         <v>47</v>
@@ -5673,32 +5647,32 @@
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C201">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D201" t="s">
+        <v>385</v>
+      </c>
+      <c r="E201" t="s">
         <v>386</v>
       </c>
-      <c r="E201" t="s">
-        <v>387</v>
-      </c>
       <c r="F201">
         <v>47</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B202">
-        <v>213</v>
-      </c>
-      <c r="C202">
-        <v>52</v>
-      </c>
-      <c r="D202" t="s">
+      <c r="B202" s="1">
+        <v>217</v>
+      </c>
+      <c r="C202" s="1">
+        <v>44</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="1" t="s">
         <v>389</v>
       </c>
       <c r="F202">
@@ -5706,16 +5680,16 @@
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B203">
-        <v>214</v>
-      </c>
-      <c r="C203">
-        <v>18</v>
-      </c>
-      <c r="D203" t="s">
+      <c r="B203" s="1">
+        <v>218</v>
+      </c>
+      <c r="C203" s="1">
+        <v>48</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F203">
@@ -5723,85 +5697,85 @@
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B204">
-        <v>215</v>
+      <c r="B204" s="1">
+        <v>219</v>
       </c>
       <c r="C204">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D204" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E204" t="s">
-        <v>393</v>
+        <v>504</v>
       </c>
       <c r="F204">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B205">
-        <v>216</v>
+      <c r="B205" s="1">
+        <v>220</v>
       </c>
       <c r="C205">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D205" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E205" t="s">
-        <v>395</v>
+        <v>505</v>
       </c>
       <c r="F205">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B206" s="1">
-        <v>217</v>
-      </c>
-      <c r="C206" s="1">
-        <v>44</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>398</v>
+        <v>221</v>
+      </c>
+      <c r="C206">
+        <v>54</v>
+      </c>
+      <c r="D206" t="s">
+        <v>399</v>
+      </c>
+      <c r="E206" t="s">
+        <v>506</v>
       </c>
       <c r="F206">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B207" s="1">
-        <v>218</v>
-      </c>
-      <c r="C207" s="1">
-        <v>48</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E207" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C207">
+        <v>34</v>
+      </c>
+      <c r="D207" t="s">
         <v>400</v>
       </c>
+      <c r="E207" t="s">
+        <v>507</v>
+      </c>
       <c r="F207">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B208" s="1">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C208">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D208" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E208" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F208">
         <v>52</v>
@@ -5809,16 +5783,16 @@
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B209" s="1">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C209">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="D209" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E209" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F209">
         <v>52</v>
@@ -5826,16 +5800,16 @@
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B210" s="1">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C210">
         <v>54</v>
       </c>
       <c r="D210" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E210" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F210">
         <v>52</v>
@@ -5843,16 +5817,16 @@
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B211" s="1">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C211">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D211" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E211" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F211">
         <v>52</v>
@@ -5860,16 +5834,16 @@
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B212" s="1">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C212">
         <v>21</v>
       </c>
       <c r="D212" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E212" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F212">
         <v>52</v>
@@ -5877,16 +5851,16 @@
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B213" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C213">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D213" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E213" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F213">
         <v>52</v>
@@ -5894,16 +5868,16 @@
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214" s="1">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C214">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D214" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E214" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F214">
         <v>52</v>
@@ -5911,16 +5885,16 @@
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" s="1">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C215">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="D215" t="s">
-        <v>413</v>
+        <v>206</v>
       </c>
       <c r="E215" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F215">
         <v>52</v>
@@ -5928,16 +5902,16 @@
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B216" s="1">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C216">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E216" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F216">
         <v>52</v>
@@ -5945,16 +5919,16 @@
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B217" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C217">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E217" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="F217">
         <v>52</v>
@@ -5962,16 +5936,16 @@
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B218" s="1">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C218">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D218" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E218" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="F218">
         <v>52</v>
@@ -5979,16 +5953,16 @@
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219" s="1">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C219">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D219" t="s">
-        <v>210</v>
+        <v>411</v>
       </c>
       <c r="E219" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F219">
         <v>52</v>
@@ -5996,16 +5970,16 @@
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B220" s="1">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C220">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D220" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E220" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="F220">
         <v>52</v>
@@ -6013,16 +5987,16 @@
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B221" s="1">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C221">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D221" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E221" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F221">
         <v>52</v>
@@ -6030,16 +6004,16 @@
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B222" s="1">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C222">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D222" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E222" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F222">
         <v>52</v>
@@ -6047,16 +6021,16 @@
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B223" s="1">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C223">
         <v>13</v>
       </c>
       <c r="D223" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E223" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="F223">
         <v>52</v>
@@ -6064,16 +6038,16 @@
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B224" s="1">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C224">
         <v>13</v>
       </c>
       <c r="D224" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E224" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F224">
         <v>52</v>
@@ -6081,16 +6055,16 @@
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B225" s="1">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C225">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D225" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E225" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F225">
         <v>52</v>
@@ -6098,16 +6072,16 @@
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B226" s="1">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C226">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D226" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E226" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="F226">
         <v>52</v>
@@ -6115,16 +6089,16 @@
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B227" s="1">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C227">
         <v>13</v>
       </c>
       <c r="D227" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E227" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F227">
         <v>52</v>
@@ -6132,16 +6106,16 @@
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B228" s="1">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C228">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D228" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E228" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F228">
         <v>52</v>
@@ -6149,16 +6123,16 @@
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B229" s="1">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C229">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D229" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E229" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="F229">
         <v>52</v>
@@ -6166,16 +6140,16 @@
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B230" s="1">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C230">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D230" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E230" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="F230">
         <v>52</v>
@@ -6183,16 +6157,16 @@
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B231" s="1">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C231">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D231" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E231" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F231">
         <v>52</v>
@@ -6200,16 +6174,16 @@
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B232" s="1">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C232">
         <v>29</v>
       </c>
       <c r="D232" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="E232" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="F232">
         <v>52</v>
@@ -6217,16 +6191,16 @@
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B233" s="1">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C233">
         <v>29</v>
       </c>
       <c r="D233" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E233" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F233">
         <v>52</v>
@@ -6234,16 +6208,16 @@
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B234" s="1">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C234">
         <v>29</v>
       </c>
       <c r="D234" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E234" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="F234">
         <v>52</v>
@@ -6251,16 +6225,16 @@
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B235" s="1">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C235">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D235" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E235" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="F235">
         <v>52</v>
@@ -6268,16 +6242,16 @@
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B236" s="1">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C236">
         <v>29</v>
       </c>
       <c r="D236" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="E236" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F236">
         <v>52</v>
@@ -6285,16 +6259,16 @@
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B237" s="1">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C237">
         <v>29</v>
       </c>
       <c r="D237" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E237" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F237">
         <v>52</v>
@@ -6302,16 +6276,16 @@
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B238" s="1">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C238">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D238" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E238" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F238">
         <v>52</v>
@@ -6319,16 +6293,16 @@
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B239" s="1">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C239">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D239" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E239" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="F239">
         <v>52</v>
@@ -6336,16 +6310,16 @@
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B240" s="1">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C240">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D240" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E240" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F240">
         <v>52</v>
@@ -6353,16 +6327,16 @@
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B241" s="1">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C241">
         <v>29</v>
       </c>
       <c r="D241" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E241" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F241">
         <v>52</v>
@@ -6370,16 +6344,16 @@
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B242" s="1">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C242">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D242" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E242" t="s">
-        <v>547</v>
+        <v>433</v>
       </c>
       <c r="F242">
         <v>52</v>
@@ -6387,16 +6361,16 @@
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B243" s="1">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C243">
         <v>29</v>
       </c>
       <c r="D243" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E243" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F243">
         <v>52</v>
@@ -6404,16 +6378,16 @@
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B244" s="1">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C244">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D244" t="s">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="E244" t="s">
-        <v>549</v>
+        <v>151</v>
       </c>
       <c r="F244">
         <v>52</v>
@@ -6421,16 +6395,16 @@
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B245" s="1">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C245">
         <v>29</v>
       </c>
       <c r="D245" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E245" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="F245">
         <v>52</v>
@@ -6438,16 +6412,16 @@
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B246" s="1">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C246">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D246" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E246" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
       <c r="F246">
         <v>52</v>
@@ -6455,16 +6429,16 @@
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B247" s="1">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C247">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D247" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E247" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F247">
         <v>52</v>
@@ -6472,16 +6446,16 @@
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B248" s="1">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C248">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D248" t="s">
-        <v>152</v>
+        <v>438</v>
       </c>
       <c r="E248" t="s">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="F248">
         <v>52</v>
@@ -6489,16 +6463,16 @@
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B249" s="1">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C249">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D249" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E249" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F249">
         <v>52</v>
@@ -6506,16 +6480,16 @@
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B250" s="1">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C250">
         <v>34</v>
       </c>
       <c r="D250" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E250" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F250">
         <v>52</v>
@@ -6523,16 +6497,16 @@
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B251" s="1">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C251">
         <v>54</v>
       </c>
       <c r="D251" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E251" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="F251">
         <v>52</v>
@@ -6540,16 +6514,16 @@
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B252" s="1">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C252">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D252" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E252" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F252">
         <v>52</v>
@@ -6557,16 +6531,16 @@
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B253" s="1">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C253">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D253" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E253" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F253">
         <v>52</v>
@@ -6574,16 +6548,16 @@
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B254" s="1">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C254">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D254" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E254" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F254">
         <v>52</v>
@@ -6591,16 +6565,16 @@
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B255" s="1">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C255">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D255" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E255" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F255">
         <v>52</v>
@@ -6608,16 +6582,16 @@
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B256" s="1">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C256">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D256" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E256" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="F256">
         <v>52</v>
@@ -6625,16 +6599,16 @@
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B257" s="1">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C257">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E257" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="F257">
         <v>52</v>
@@ -6642,16 +6616,16 @@
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B258" s="1">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C258">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="D258" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E258" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F258">
         <v>52</v>
@@ -6659,16 +6633,16 @@
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B259" s="1">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C259">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D259" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E259" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F259">
         <v>52</v>
@@ -6676,16 +6650,16 @@
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B260" s="1">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C260">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D260" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E260" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="F260">
         <v>52</v>
@@ -6693,16 +6667,16 @@
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B261" s="1">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C261">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D261" t="s">
-        <v>456</v>
+        <v>372</v>
       </c>
       <c r="E261" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="F261">
         <v>52</v>
@@ -6710,16 +6684,16 @@
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B262" s="1">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C262">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D262" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E262" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F262">
         <v>52</v>
@@ -6727,16 +6701,16 @@
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B263" s="1">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C263">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D263" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E263" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F263">
         <v>52</v>
@@ -6744,16 +6718,16 @@
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B264" s="1">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C264">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D264" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E264" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="F264">
         <v>52</v>
@@ -6761,16 +6735,16 @@
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B265" s="1">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C265">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D265" t="s">
-        <v>381</v>
+        <v>454</v>
       </c>
       <c r="E265" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F265">
         <v>52</v>
@@ -6778,16 +6752,16 @@
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B266" s="1">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C266">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D266" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E266" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F266">
         <v>52</v>
@@ -6795,16 +6769,16 @@
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B267" s="1">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C267">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D267" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E267" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="F267">
         <v>52</v>
@@ -6812,16 +6786,16 @@
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B268" s="1">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C268">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D268" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E268" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="F268">
         <v>52</v>
@@ -6829,16 +6803,16 @@
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B269" s="1">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C269">
         <v>13</v>
       </c>
       <c r="D269" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E269" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F269">
         <v>52</v>
@@ -6846,16 +6820,16 @@
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B270" s="1">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C270">
         <v>13</v>
       </c>
       <c r="D270" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E270" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="F270">
         <v>52</v>
@@ -6863,16 +6837,16 @@
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B271" s="1">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C271">
         <v>13</v>
       </c>
       <c r="D271" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E271" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F271">
         <v>52</v>
@@ -6880,16 +6854,16 @@
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B272" s="1">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C272">
         <v>13</v>
       </c>
       <c r="D272" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E272" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F272">
         <v>52</v>
@@ -6897,16 +6871,16 @@
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="1">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C273">
         <v>13</v>
       </c>
       <c r="D273" t="s">
-        <v>467</v>
+        <v>104</v>
       </c>
       <c r="E273" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F273">
         <v>52</v>
@@ -6914,16 +6888,16 @@
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B274" s="1">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C274">
         <v>13</v>
       </c>
       <c r="D274" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E274" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F274">
         <v>52</v>
@@ -6931,16 +6905,16 @@
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B275" s="1">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C275">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D275" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E275" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F275">
         <v>52</v>
@@ -6948,16 +6922,16 @@
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B276" s="1">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C276">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D276" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E276" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F276">
         <v>52</v>
@@ -6965,16 +6939,16 @@
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B277" s="1">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C277">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D277" t="s">
-        <v>106</v>
+        <v>465</v>
       </c>
       <c r="E277" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="F277">
         <v>52</v>
@@ -6982,16 +6956,16 @@
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278" s="1">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C278">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D278" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E278" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="F278">
         <v>52</v>
@@ -6999,16 +6973,16 @@
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B279" s="1">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C279">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D279" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E279" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="F279">
         <v>52</v>
@@ -7016,16 +6990,16 @@
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B280" s="1">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C280">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D280" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E280" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F280">
         <v>52</v>
@@ -7033,16 +7007,16 @@
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B281" s="1">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C281">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D281" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E281" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F281">
         <v>52</v>
@@ -7050,16 +7024,16 @@
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B282" s="1">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C282">
         <v>20</v>
       </c>
       <c r="D282" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E282" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F282">
         <v>52</v>
@@ -7067,16 +7041,16 @@
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B283" s="1">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C283">
         <v>20</v>
       </c>
       <c r="D283" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E283" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F283">
         <v>52</v>
@@ -7084,16 +7058,16 @@
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B284" s="1">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C284">
         <v>20</v>
       </c>
       <c r="D284" t="s">
-        <v>477</v>
+        <v>381</v>
       </c>
       <c r="E284" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F284">
         <v>52</v>
@@ -7101,16 +7075,16 @@
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B285" s="1">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C285">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D285" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E285" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="F285">
         <v>52</v>
@@ -7118,16 +7092,16 @@
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B286" s="1">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C286">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D286" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E286" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="F286">
         <v>52</v>
@@ -7135,16 +7109,16 @@
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B287" s="1">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C287">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D287" t="s">
-        <v>480</v>
+        <v>158</v>
       </c>
       <c r="E287" t="s">
-        <v>590</v>
+        <v>159</v>
       </c>
       <c r="F287">
         <v>52</v>
@@ -7152,16 +7126,16 @@
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B288" s="1">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C288">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D288" t="s">
-        <v>390</v>
+        <v>474</v>
       </c>
       <c r="E288" t="s">
-        <v>591</v>
+        <v>474</v>
       </c>
       <c r="F288">
         <v>52</v>
@@ -7169,16 +7143,16 @@
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B289" s="1">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C289">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D289" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E289" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="F289">
         <v>52</v>
@@ -7186,16 +7160,16 @@
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B290" s="1">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C290">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D290" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E290" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="F290">
         <v>52</v>
@@ -7203,16 +7177,16 @@
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B291" s="1">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C291">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D291" t="s">
-        <v>162</v>
+        <v>477</v>
       </c>
       <c r="E291" t="s">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="F291">
         <v>52</v>
@@ -7220,16 +7194,16 @@
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B292" s="1">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C292">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D292" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E292" t="s">
-        <v>483</v>
+        <v>588</v>
       </c>
       <c r="F292">
         <v>52</v>
@@ -7237,16 +7211,16 @@
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B293" s="1">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C293">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D293" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E293" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F293">
         <v>52</v>
@@ -7254,16 +7228,16 @@
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B294" s="1">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C294">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D294" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E294" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F294">
         <v>52</v>
@@ -7271,16 +7245,16 @@
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B295" s="1">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C295">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D295" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E295" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="F295">
         <v>52</v>
@@ -7288,16 +7262,16 @@
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B296" s="1">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C296">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D296" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E296" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="F296">
         <v>52</v>
@@ -7305,16 +7279,16 @@
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B297" s="1">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C297">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D297" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E297" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="F297">
         <v>52</v>
@@ -7322,16 +7296,16 @@
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B298" s="1">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C298">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D298" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E298" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="F298">
         <v>52</v>
@@ -7339,16 +7313,16 @@
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B299" s="1">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C299">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D299" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="E299" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="F299">
         <v>52</v>
@@ -7356,16 +7330,16 @@
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B300" s="1">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C300">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D300" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E300" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="F300">
         <v>52</v>
@@ -7373,16 +7347,16 @@
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B301" s="1">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C301">
         <v>34</v>
       </c>
       <c r="D301" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="E301" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="F301">
         <v>52</v>
@@ -7390,16 +7364,16 @@
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B302" s="1">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C302">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D302" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E302" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="F302">
         <v>52</v>
@@ -7407,16 +7381,16 @@
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B303" s="1">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C303">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D303" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E303" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="F303">
         <v>52</v>
@@ -7424,16 +7398,16 @@
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B304" s="1">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C304">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D304" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E304" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="F304">
         <v>52</v>
@@ -7441,16 +7415,16 @@
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B305" s="1">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C305">
         <v>34</v>
       </c>
       <c r="D305" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E305" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="F305">
         <v>52</v>
@@ -7458,16 +7432,16 @@
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B306" s="1">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C306">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D306" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E306" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="F306">
         <v>52</v>
@@ -7475,16 +7449,16 @@
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B307" s="1">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C307">
         <v>34</v>
       </c>
       <c r="D307" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E307" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="F307">
         <v>52</v>
@@ -7492,16 +7466,16 @@
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B308" s="1">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C308">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D308" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E308" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="F308">
         <v>52</v>
@@ -7509,16 +7483,16 @@
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B309" s="1">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C309">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D309" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E309" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="F309">
         <v>52</v>
@@ -7526,16 +7500,16 @@
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B310" s="1">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C310">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D310" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E310" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="F310">
         <v>52</v>
@@ -7543,16 +7517,16 @@
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B311" s="1">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C311">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D311" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E311" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="F311">
         <v>52</v>
@@ -7560,16 +7534,16 @@
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B312" s="1">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C312">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D312" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E312" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F312">
         <v>52</v>
@@ -7577,16 +7551,16 @@
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B313" s="1">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C313">
         <v>55</v>
       </c>
       <c r="D313" t="s">
-        <v>504</v>
+        <v>440</v>
       </c>
       <c r="E313" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="F313">
         <v>52</v>
@@ -7594,16 +7568,16 @@
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B314" s="1">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C314">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D314" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E314" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="F314">
         <v>52</v>
@@ -7611,16 +7585,16 @@
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B315" s="1">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C315">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D315" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E315" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="F315">
         <v>52</v>
@@ -7628,16 +7602,16 @@
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B316" s="1">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C316">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D316" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E316" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="F316">
         <v>52</v>
@@ -7645,16 +7619,16 @@
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B317" s="1">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C317">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D317" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="E317" t="s">
-        <v>557</v>
+        <v>612</v>
       </c>
       <c r="F317">
         <v>52</v>
@@ -7662,86 +7636,18 @@
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B318" s="1">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C318">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D318" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E318" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="F318">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B319" s="1">
-        <v>330</v>
-      </c>
-      <c r="C319">
-        <v>20</v>
-      </c>
-      <c r="D319" t="s">
-        <v>509</v>
-      </c>
-      <c r="E319" t="s">
-        <v>619</v>
-      </c>
-      <c r="F319">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B320" s="1">
-        <v>331</v>
-      </c>
-      <c r="C320">
-        <v>66</v>
-      </c>
-      <c r="D320" t="s">
-        <v>510</v>
-      </c>
-      <c r="E320" t="s">
-        <v>620</v>
-      </c>
-      <c r="F320">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B321" s="1">
-        <v>332</v>
-      </c>
-      <c r="C321">
-        <v>64</v>
-      </c>
-      <c r="D321" t="s">
-        <v>511</v>
-      </c>
-      <c r="E321" t="s">
-        <v>621</v>
-      </c>
-      <c r="F321">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B322" s="1">
-        <v>333</v>
-      </c>
-      <c r="C322">
-        <v>68</v>
-      </c>
-      <c r="D322" t="s">
-        <v>512</v>
-      </c>
-      <c r="E322" t="s">
-        <v>622</v>
-      </c>
-      <c r="F322">
         <v>52</v>
       </c>
     </row>

--- a/db/data/office_items.xlsx
+++ b/db/data/office_items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1499A608-33F4-4C7A-93B4-A9298D88A21C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BA0712-B91A-4C7D-A23A-C633F689A677}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2276,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,7 +2293,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,7 +2310,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2327,7 +2327,7 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>13</v>
       </c>
       <c r="F6">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2361,7 +2361,7 @@
         <v>15</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2378,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2395,7 +2395,7 @@
         <v>19</v>
       </c>
       <c r="F9">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,7 +2412,7 @@
         <v>21</v>
       </c>
       <c r="F10">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2429,7 +2429,7 @@
         <v>23</v>
       </c>
       <c r="F11">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,7 +2446,7 @@
         <v>25</v>
       </c>
       <c r="F12">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,7 +2463,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>29</v>
       </c>
       <c r="F14">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>31</v>
       </c>
       <c r="F15">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2514,7 +2514,7 @@
         <v>33</v>
       </c>
       <c r="F16">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -2531,7 +2531,7 @@
         <v>35</v>
       </c>
       <c r="F17">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>37</v>
       </c>
       <c r="F18">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -2565,7 +2565,7 @@
         <v>39</v>
       </c>
       <c r="F19">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -2582,7 +2582,7 @@
         <v>41</v>
       </c>
       <c r="F20">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -2599,7 +2599,7 @@
         <v>43</v>
       </c>
       <c r="F21">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
@@ -2616,7 +2616,7 @@
         <v>45</v>
       </c>
       <c r="F22">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
@@ -2633,7 +2633,7 @@
         <v>47</v>
       </c>
       <c r="F23">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
@@ -2650,7 +2650,7 @@
         <v>49</v>
       </c>
       <c r="F24">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
@@ -2667,7 +2667,7 @@
         <v>51</v>
       </c>
       <c r="F25">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
@@ -2684,7 +2684,7 @@
         <v>53</v>
       </c>
       <c r="F26">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
@@ -2701,7 +2701,7 @@
         <v>55</v>
       </c>
       <c r="F27">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
@@ -2718,7 +2718,7 @@
         <v>57</v>
       </c>
       <c r="F28">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
@@ -2735,7 +2735,7 @@
         <v>59</v>
       </c>
       <c r="F29">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
@@ -2752,7 +2752,7 @@
         <v>395</v>
       </c>
       <c r="F30">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
@@ -2769,7 +2769,7 @@
         <v>61</v>
       </c>
       <c r="F31">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
@@ -2786,7 +2786,7 @@
         <v>63</v>
       </c>
       <c r="F32">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
@@ -2803,7 +2803,7 @@
         <v>65</v>
       </c>
       <c r="F33">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
@@ -2820,7 +2820,7 @@
         <v>67</v>
       </c>
       <c r="F34">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
@@ -2837,7 +2837,7 @@
         <v>69</v>
       </c>
       <c r="F35">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
@@ -2854,7 +2854,7 @@
         <v>71</v>
       </c>
       <c r="F36">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
@@ -2871,7 +2871,7 @@
         <v>73</v>
       </c>
       <c r="F37">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
@@ -2888,7 +2888,7 @@
         <v>75</v>
       </c>
       <c r="F38">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
@@ -2905,7 +2905,7 @@
         <v>77</v>
       </c>
       <c r="F39">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
@@ -2922,7 +2922,7 @@
         <v>79</v>
       </c>
       <c r="F40">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
@@ -2939,7 +2939,7 @@
         <v>81</v>
       </c>
       <c r="F41">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
@@ -2956,7 +2956,7 @@
         <v>83</v>
       </c>
       <c r="F42">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
@@ -2973,7 +2973,7 @@
         <v>85</v>
       </c>
       <c r="F43">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
@@ -2990,7 +2990,7 @@
         <v>87</v>
       </c>
       <c r="F44">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
@@ -3007,7 +3007,7 @@
         <v>89</v>
       </c>
       <c r="F45">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
@@ -3024,7 +3024,7 @@
         <v>91</v>
       </c>
       <c r="F46">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
@@ -3041,7 +3041,7 @@
         <v>93</v>
       </c>
       <c r="F47">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
@@ -3058,7 +3058,7 @@
         <v>95</v>
       </c>
       <c r="F48">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
@@ -3075,7 +3075,7 @@
         <v>97</v>
       </c>
       <c r="F49">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
@@ -3092,7 +3092,7 @@
         <v>99</v>
       </c>
       <c r="F50">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
@@ -3109,7 +3109,7 @@
         <v>101</v>
       </c>
       <c r="F51">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>103</v>
       </c>
       <c r="F52">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
@@ -3143,7 +3143,7 @@
         <v>105</v>
       </c>
       <c r="F53">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
@@ -3160,7 +3160,7 @@
         <v>47</v>
       </c>
       <c r="F54">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
@@ -3177,7 +3177,7 @@
         <v>107</v>
       </c>
       <c r="F55">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
@@ -3194,7 +3194,7 @@
         <v>109</v>
       </c>
       <c r="F56">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
@@ -3211,7 +3211,7 @@
         <v>111</v>
       </c>
       <c r="F57">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
@@ -3228,7 +3228,7 @@
         <v>113</v>
       </c>
       <c r="F58">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
@@ -3245,7 +3245,7 @@
         <v>115</v>
       </c>
       <c r="F59">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
@@ -3262,7 +3262,7 @@
         <v>117</v>
       </c>
       <c r="F60">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
@@ -3279,7 +3279,7 @@
         <v>119</v>
       </c>
       <c r="F61">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
@@ -3296,7 +3296,7 @@
         <v>121</v>
       </c>
       <c r="F62">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
@@ -3313,7 +3313,7 @@
         <v>123</v>
       </c>
       <c r="F63">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
@@ -3330,7 +3330,7 @@
         <v>125</v>
       </c>
       <c r="F64">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
@@ -3347,7 +3347,7 @@
         <v>127</v>
       </c>
       <c r="F65">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
@@ -3364,7 +3364,7 @@
         <v>129</v>
       </c>
       <c r="F66">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
@@ -3381,7 +3381,7 @@
         <v>131</v>
       </c>
       <c r="F67">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
@@ -3398,7 +3398,7 @@
         <v>133</v>
       </c>
       <c r="F68">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
@@ -3415,7 +3415,7 @@
         <v>135</v>
       </c>
       <c r="F69">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
@@ -3432,7 +3432,7 @@
         <v>137</v>
       </c>
       <c r="F70">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
@@ -3449,7 +3449,7 @@
         <v>139</v>
       </c>
       <c r="F71">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
@@ -3466,7 +3466,7 @@
         <v>141</v>
       </c>
       <c r="F72">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
@@ -3483,7 +3483,7 @@
         <v>143</v>
       </c>
       <c r="F73">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>145</v>
       </c>
       <c r="F74">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
@@ -3517,7 +3517,7 @@
         <v>147</v>
       </c>
       <c r="F75">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>149</v>
       </c>
       <c r="F76">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
@@ -3551,7 +3551,7 @@
         <v>151</v>
       </c>
       <c r="F77">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
@@ -3568,7 +3568,7 @@
         <v>153</v>
       </c>
       <c r="F78">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -3585,7 +3585,7 @@
         <v>155</v>
       </c>
       <c r="F79">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
@@ -3602,7 +3602,7 @@
         <v>157</v>
       </c>
       <c r="F80">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
@@ -3619,7 +3619,7 @@
         <v>159</v>
       </c>
       <c r="F81">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
@@ -3636,7 +3636,7 @@
         <v>161</v>
       </c>
       <c r="F82">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
@@ -3653,7 +3653,7 @@
         <v>163</v>
       </c>
       <c r="F83">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
@@ -3670,7 +3670,7 @@
         <v>165</v>
       </c>
       <c r="F84">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
@@ -3687,7 +3687,7 @@
         <v>167</v>
       </c>
       <c r="F85">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
@@ -3704,7 +3704,7 @@
         <v>169</v>
       </c>
       <c r="F86">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
@@ -3721,7 +3721,7 @@
         <v>171</v>
       </c>
       <c r="F87">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
@@ -3738,7 +3738,7 @@
         <v>173</v>
       </c>
       <c r="F88">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
@@ -3755,7 +3755,7 @@
         <v>175</v>
       </c>
       <c r="F89">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>177</v>
       </c>
       <c r="F90">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
@@ -3789,7 +3789,7 @@
         <v>179</v>
       </c>
       <c r="F91">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
         <v>181</v>
       </c>
       <c r="F92">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
@@ -3823,7 +3823,7 @@
         <v>183</v>
       </c>
       <c r="F93">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
@@ -3840,7 +3840,7 @@
         <v>185</v>
       </c>
       <c r="F94">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
@@ -3857,7 +3857,7 @@
         <v>107</v>
       </c>
       <c r="F95">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
@@ -3874,7 +3874,7 @@
         <v>393</v>
       </c>
       <c r="F96">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.25">
@@ -3891,7 +3891,7 @@
         <v>187</v>
       </c>
       <c r="F97">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.25">
@@ -3908,7 +3908,7 @@
         <v>189</v>
       </c>
       <c r="F98">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>149</v>
       </c>
       <c r="F99">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
@@ -3942,7 +3942,7 @@
         <v>191</v>
       </c>
       <c r="F100">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.25">
@@ -3959,7 +3959,7 @@
         <v>193</v>
       </c>
       <c r="F101">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.25">
@@ -3976,7 +3976,7 @@
         <v>195</v>
       </c>
       <c r="F102">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>197</v>
       </c>
       <c r="F103">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
@@ -4010,7 +4010,7 @@
         <v>199</v>
       </c>
       <c r="F104">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.25">
@@ -4027,7 +4027,7 @@
         <v>201</v>
       </c>
       <c r="F105">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
@@ -4044,7 +4044,7 @@
         <v>203</v>
       </c>
       <c r="F106">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>205</v>
       </c>
       <c r="F107">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
@@ -4078,7 +4078,7 @@
         <v>207</v>
       </c>
       <c r="F108">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.25">
@@ -4095,7 +4095,7 @@
         <v>209</v>
       </c>
       <c r="F109">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
@@ -4112,7 +4112,7 @@
         <v>211</v>
       </c>
       <c r="F110">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
@@ -4129,7 +4129,7 @@
         <v>213</v>
       </c>
       <c r="F111">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
         <v>215</v>
       </c>
       <c r="F112">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
@@ -4163,7 +4163,7 @@
         <v>217</v>
       </c>
       <c r="F113">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
@@ -4180,7 +4180,7 @@
         <v>219</v>
       </c>
       <c r="F114">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
@@ -4197,7 +4197,7 @@
         <v>221</v>
       </c>
       <c r="F115">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
@@ -4214,7 +4214,7 @@
         <v>223</v>
       </c>
       <c r="F116">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
@@ -4231,7 +4231,7 @@
         <v>225</v>
       </c>
       <c r="F117">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
@@ -4248,7 +4248,7 @@
         <v>226</v>
       </c>
       <c r="F118">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
@@ -4265,7 +4265,7 @@
         <v>228</v>
       </c>
       <c r="F119">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
@@ -4282,7 +4282,7 @@
         <v>230</v>
       </c>
       <c r="F120">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
@@ -4299,7 +4299,7 @@
         <v>232</v>
       </c>
       <c r="F121">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
@@ -4316,7 +4316,7 @@
         <v>234</v>
       </c>
       <c r="F122">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>236</v>
       </c>
       <c r="F123">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
@@ -4350,7 +4350,7 @@
         <v>238</v>
       </c>
       <c r="F124">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
@@ -4367,7 +4367,7 @@
         <v>240</v>
       </c>
       <c r="F125">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
@@ -4384,7 +4384,7 @@
         <v>242</v>
       </c>
       <c r="F126">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
@@ -4401,7 +4401,7 @@
         <v>244</v>
       </c>
       <c r="F127">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>246</v>
       </c>
       <c r="F128">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
         <v>248</v>
       </c>
       <c r="F129">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
@@ -4452,7 +4452,7 @@
         <v>250</v>
       </c>
       <c r="F130">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
@@ -4469,7 +4469,7 @@
         <v>252</v>
       </c>
       <c r="F131">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
@@ -4486,7 +4486,7 @@
         <v>254</v>
       </c>
       <c r="F132">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
@@ -4503,7 +4503,7 @@
         <v>256</v>
       </c>
       <c r="F133">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
@@ -4520,7 +4520,7 @@
         <v>258</v>
       </c>
       <c r="F134">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
@@ -4537,7 +4537,7 @@
         <v>260</v>
       </c>
       <c r="F135">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
@@ -4554,7 +4554,7 @@
         <v>262</v>
       </c>
       <c r="F136">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
@@ -4571,7 +4571,7 @@
         <v>264</v>
       </c>
       <c r="F137">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.25">
@@ -4588,7 +4588,7 @@
         <v>266</v>
       </c>
       <c r="F138">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>268</v>
       </c>
       <c r="F139">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
@@ -4622,7 +4622,7 @@
         <v>270</v>
       </c>
       <c r="F140">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
@@ -4639,7 +4639,7 @@
         <v>272</v>
       </c>
       <c r="F141">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
@@ -4656,7 +4656,7 @@
         <v>274</v>
       </c>
       <c r="F142">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
@@ -4673,7 +4673,7 @@
         <v>276</v>
       </c>
       <c r="F143">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
@@ -4690,7 +4690,7 @@
         <v>278</v>
       </c>
       <c r="F144">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.25">
@@ -4707,7 +4707,7 @@
         <v>280</v>
       </c>
       <c r="F145">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.25">
@@ -4724,7 +4724,7 @@
         <v>282</v>
       </c>
       <c r="F146">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>284</v>
       </c>
       <c r="F147">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
@@ -4758,7 +4758,7 @@
         <v>286</v>
       </c>
       <c r="F148">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.25">
@@ -4775,7 +4775,7 @@
         <v>288</v>
       </c>
       <c r="F149">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.25">
@@ -4792,7 +4792,7 @@
         <v>290</v>
       </c>
       <c r="F150">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>292</v>
       </c>
       <c r="F151">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.25">
@@ -4826,7 +4826,7 @@
         <v>294</v>
       </c>
       <c r="F152">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.25">
@@ -4843,7 +4843,7 @@
         <v>296</v>
       </c>
       <c r="F153">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>298</v>
       </c>
       <c r="F154">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>300</v>
       </c>
       <c r="F155">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
@@ -4894,7 +4894,7 @@
         <v>302</v>
       </c>
       <c r="F156">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.25">
@@ -4911,7 +4911,7 @@
         <v>303</v>
       </c>
       <c r="F157">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
@@ -4928,7 +4928,7 @@
         <v>305</v>
       </c>
       <c r="F158">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>307</v>
       </c>
       <c r="F159">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>309</v>
       </c>
       <c r="F160">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
@@ -4979,7 +4979,7 @@
         <v>615</v>
       </c>
       <c r="F161">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
@@ -4996,7 +4996,7 @@
         <v>311</v>
       </c>
       <c r="F162">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>313</v>
       </c>
       <c r="F163">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
@@ -5030,7 +5030,7 @@
         <v>315</v>
       </c>
       <c r="F164">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
         <v>317</v>
       </c>
       <c r="F165">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>319</v>
       </c>
       <c r="F166">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
@@ -5081,7 +5081,7 @@
         <v>321</v>
       </c>
       <c r="F167">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
@@ -5098,7 +5098,7 @@
         <v>323</v>
       </c>
       <c r="F168">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
@@ -5115,7 +5115,7 @@
         <v>325</v>
       </c>
       <c r="F169">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>327</v>
       </c>
       <c r="F170">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
@@ -5149,7 +5149,7 @@
         <v>329</v>
       </c>
       <c r="F171">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
@@ -5166,7 +5166,7 @@
         <v>331</v>
       </c>
       <c r="F172">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
@@ -5183,7 +5183,7 @@
         <v>333</v>
       </c>
       <c r="F173">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
@@ -5200,7 +5200,7 @@
         <v>335</v>
       </c>
       <c r="F174">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
@@ -5217,7 +5217,7 @@
         <v>337</v>
       </c>
       <c r="F175">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
@@ -5234,7 +5234,7 @@
         <v>339</v>
       </c>
       <c r="F176">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
@@ -5251,7 +5251,7 @@
         <v>341</v>
       </c>
       <c r="F177">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.25">
@@ -5268,7 +5268,7 @@
         <v>343</v>
       </c>
       <c r="F178">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.25">
@@ -5285,7 +5285,7 @@
         <v>345</v>
       </c>
       <c r="F179">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.25">
@@ -5302,7 +5302,7 @@
         <v>347</v>
       </c>
       <c r="F180">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.25">
@@ -5319,7 +5319,7 @@
         <v>349</v>
       </c>
       <c r="F181">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.25">
@@ -5336,7 +5336,7 @@
         <v>351</v>
       </c>
       <c r="F182">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>353</v>
       </c>
       <c r="F183">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.25">
@@ -5370,7 +5370,7 @@
         <v>355</v>
       </c>
       <c r="F184">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>357</v>
       </c>
       <c r="F185">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.25">
@@ -5404,7 +5404,7 @@
         <v>359</v>
       </c>
       <c r="F186">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.25">
@@ -5421,7 +5421,7 @@
         <v>361</v>
       </c>
       <c r="F187">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.25">
@@ -5438,7 +5438,7 @@
         <v>363</v>
       </c>
       <c r="F188">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>365</v>
       </c>
       <c r="F189">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.25">
@@ -5472,7 +5472,7 @@
         <v>367</v>
       </c>
       <c r="F190">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.25">
@@ -5489,7 +5489,7 @@
         <v>369</v>
       </c>
       <c r="F191">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>371</v>
       </c>
       <c r="F192">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
@@ -5523,7 +5523,7 @@
         <v>373</v>
       </c>
       <c r="F193">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
@@ -5540,7 +5540,7 @@
         <v>375</v>
       </c>
       <c r="F194">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
@@ -5557,7 +5557,7 @@
         <v>109</v>
       </c>
       <c r="F195">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
@@ -5574,7 +5574,7 @@
         <v>185</v>
       </c>
       <c r="F196">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
@@ -5591,7 +5591,7 @@
         <v>378</v>
       </c>
       <c r="F197">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
@@ -5608,7 +5608,7 @@
         <v>380</v>
       </c>
       <c r="F198">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
@@ -5625,7 +5625,7 @@
         <v>382</v>
       </c>
       <c r="F199">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
@@ -5642,7 +5642,7 @@
         <v>384</v>
       </c>
       <c r="F200">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
@@ -5659,7 +5659,7 @@
         <v>386</v>
       </c>
       <c r="F201">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
@@ -5676,7 +5676,7 @@
         <v>389</v>
       </c>
       <c r="F202">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>391</v>
       </c>
       <c r="F203">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
@@ -5710,7 +5710,7 @@
         <v>504</v>
       </c>
       <c r="F204">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
@@ -5727,7 +5727,7 @@
         <v>505</v>
       </c>
       <c r="F205">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
@@ -5744,7 +5744,7 @@
         <v>506</v>
       </c>
       <c r="F206">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>507</v>
       </c>
       <c r="F207">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
@@ -5778,7 +5778,7 @@
         <v>508</v>
       </c>
       <c r="F208">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.25">
@@ -5795,7 +5795,7 @@
         <v>509</v>
       </c>
       <c r="F209">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.25">
@@ -5812,7 +5812,7 @@
         <v>510</v>
       </c>
       <c r="F210">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.25">
@@ -5829,7 +5829,7 @@
         <v>511</v>
       </c>
       <c r="F211">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.25">
@@ -5846,7 +5846,7 @@
         <v>512</v>
       </c>
       <c r="F212">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.25">
@@ -5863,7 +5863,7 @@
         <v>513</v>
       </c>
       <c r="F213">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
@@ -5880,7 +5880,7 @@
         <v>514</v>
       </c>
       <c r="F214">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
@@ -5897,7 +5897,7 @@
         <v>515</v>
       </c>
       <c r="F215">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.25">
@@ -5914,7 +5914,7 @@
         <v>516</v>
       </c>
       <c r="F216">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.25">
@@ -5931,7 +5931,7 @@
         <v>517</v>
       </c>
       <c r="F217">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.25">
@@ -5948,7 +5948,7 @@
         <v>518</v>
       </c>
       <c r="F218">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
@@ -5965,7 +5965,7 @@
         <v>519</v>
       </c>
       <c r="F219">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.25">
@@ -5982,7 +5982,7 @@
         <v>520</v>
       </c>
       <c r="F220">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.25">
@@ -5999,7 +5999,7 @@
         <v>521</v>
       </c>
       <c r="F221">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.25">
@@ -6016,7 +6016,7 @@
         <v>522</v>
       </c>
       <c r="F222">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>523</v>
       </c>
       <c r="F223">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.25">
@@ -6050,7 +6050,7 @@
         <v>524</v>
       </c>
       <c r="F224">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.25">
@@ -6067,7 +6067,7 @@
         <v>525</v>
       </c>
       <c r="F225">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.25">
@@ -6084,7 +6084,7 @@
         <v>526</v>
       </c>
       <c r="F226">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.25">
@@ -6101,7 +6101,7 @@
         <v>527</v>
       </c>
       <c r="F227">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.25">
@@ -6118,7 +6118,7 @@
         <v>528</v>
       </c>
       <c r="F228">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.25">
@@ -6135,7 +6135,7 @@
         <v>529</v>
       </c>
       <c r="F229">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.25">
@@ -6152,7 +6152,7 @@
         <v>530</v>
       </c>
       <c r="F230">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.25">
@@ -6169,7 +6169,7 @@
         <v>531</v>
       </c>
       <c r="F231">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.25">
@@ -6186,7 +6186,7 @@
         <v>532</v>
       </c>
       <c r="F232">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.25">
@@ -6203,7 +6203,7 @@
         <v>533</v>
       </c>
       <c r="F233">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
@@ -6220,7 +6220,7 @@
         <v>534</v>
       </c>
       <c r="F234">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
@@ -6237,7 +6237,7 @@
         <v>535</v>
       </c>
       <c r="F235">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
@@ -6254,7 +6254,7 @@
         <v>536</v>
       </c>
       <c r="F236">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
@@ -6271,7 +6271,7 @@
         <v>537</v>
       </c>
       <c r="F237">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
@@ -6288,7 +6288,7 @@
         <v>538</v>
       </c>
       <c r="F238">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
@@ -6305,7 +6305,7 @@
         <v>539</v>
       </c>
       <c r="F239">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
@@ -6322,7 +6322,7 @@
         <v>540</v>
       </c>
       <c r="F240">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.25">
@@ -6339,7 +6339,7 @@
         <v>541</v>
       </c>
       <c r="F241">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.25">
@@ -6356,7 +6356,7 @@
         <v>433</v>
       </c>
       <c r="F242">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.25">
@@ -6373,7 +6373,7 @@
         <v>542</v>
       </c>
       <c r="F243">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.25">
@@ -6390,7 +6390,7 @@
         <v>151</v>
       </c>
       <c r="F244">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.25">
@@ -6407,7 +6407,7 @@
         <v>543</v>
       </c>
       <c r="F245">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.25">
@@ -6424,7 +6424,7 @@
         <v>544</v>
       </c>
       <c r="F246">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.25">
@@ -6441,7 +6441,7 @@
         <v>545</v>
       </c>
       <c r="F247">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.25">
@@ -6458,7 +6458,7 @@
         <v>546</v>
       </c>
       <c r="F248">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.25">
@@ -6475,7 +6475,7 @@
         <v>547</v>
       </c>
       <c r="F249">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.25">
@@ -6492,7 +6492,7 @@
         <v>548</v>
       </c>
       <c r="F250">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.25">
@@ -6509,7 +6509,7 @@
         <v>549</v>
       </c>
       <c r="F251">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.25">
@@ -6526,7 +6526,7 @@
         <v>550</v>
       </c>
       <c r="F252">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.25">
@@ -6543,7 +6543,7 @@
         <v>551</v>
       </c>
       <c r="F253">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.25">
@@ -6560,7 +6560,7 @@
         <v>552</v>
       </c>
       <c r="F254">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.25">
@@ -6577,7 +6577,7 @@
         <v>553</v>
       </c>
       <c r="F255">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.25">
@@ -6594,7 +6594,7 @@
         <v>554</v>
       </c>
       <c r="F256">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.25">
@@ -6611,7 +6611,7 @@
         <v>555</v>
       </c>
       <c r="F257">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.25">
@@ -6628,7 +6628,7 @@
         <v>556</v>
       </c>
       <c r="F258">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.25">
@@ -6645,7 +6645,7 @@
         <v>557</v>
       </c>
       <c r="F259">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.25">
@@ -6662,7 +6662,7 @@
         <v>558</v>
       </c>
       <c r="F260">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.25">
@@ -6679,7 +6679,7 @@
         <v>559</v>
       </c>
       <c r="F261">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.25">
@@ -6696,7 +6696,7 @@
         <v>560</v>
       </c>
       <c r="F262">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
         <v>561</v>
       </c>
       <c r="F263">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.25">
@@ -6730,7 +6730,7 @@
         <v>562</v>
       </c>
       <c r="F264">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.25">
@@ -6747,7 +6747,7 @@
         <v>563</v>
       </c>
       <c r="F265">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.25">
@@ -6764,7 +6764,7 @@
         <v>564</v>
       </c>
       <c r="F266">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.25">
@@ -6781,7 +6781,7 @@
         <v>565</v>
       </c>
       <c r="F267">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.25">
@@ -6798,7 +6798,7 @@
         <v>566</v>
       </c>
       <c r="F268">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.25">
@@ -6815,7 +6815,7 @@
         <v>567</v>
       </c>
       <c r="F269">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.25">
@@ -6832,7 +6832,7 @@
         <v>568</v>
       </c>
       <c r="F270">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.25">
@@ -6849,7 +6849,7 @@
         <v>569</v>
       </c>
       <c r="F271">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.25">
@@ -6866,7 +6866,7 @@
         <v>570</v>
       </c>
       <c r="F272">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.25">
@@ -6883,7 +6883,7 @@
         <v>571</v>
       </c>
       <c r="F273">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.25">
@@ -6900,7 +6900,7 @@
         <v>572</v>
       </c>
       <c r="F274">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.25">
@@ -6917,7 +6917,7 @@
         <v>573</v>
       </c>
       <c r="F275">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
         <v>574</v>
       </c>
       <c r="F276">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
@@ -6951,7 +6951,7 @@
         <v>575</v>
       </c>
       <c r="F277">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
@@ -6968,7 +6968,7 @@
         <v>576</v>
       </c>
       <c r="F278">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.25">
@@ -6985,7 +6985,7 @@
         <v>577</v>
       </c>
       <c r="F279">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.25">
@@ -7002,7 +7002,7 @@
         <v>578</v>
       </c>
       <c r="F280">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.25">
@@ -7019,7 +7019,7 @@
         <v>579</v>
       </c>
       <c r="F281">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.25">
@@ -7036,7 +7036,7 @@
         <v>580</v>
       </c>
       <c r="F282">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>581</v>
       </c>
       <c r="F283">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.25">
@@ -7070,7 +7070,7 @@
         <v>582</v>
       </c>
       <c r="F284">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.25">
@@ -7087,7 +7087,7 @@
         <v>583</v>
       </c>
       <c r="F285">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.25">
@@ -7104,7 +7104,7 @@
         <v>584</v>
       </c>
       <c r="F286">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.25">
@@ -7121,7 +7121,7 @@
         <v>159</v>
       </c>
       <c r="F287">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.25">
@@ -7138,7 +7138,7 @@
         <v>474</v>
       </c>
       <c r="F288">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.25">
@@ -7155,7 +7155,7 @@
         <v>585</v>
       </c>
       <c r="F289">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.25">
@@ -7172,7 +7172,7 @@
         <v>586</v>
       </c>
       <c r="F290">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.25">
@@ -7189,7 +7189,7 @@
         <v>587</v>
       </c>
       <c r="F291">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.25">
@@ -7206,7 +7206,7 @@
         <v>588</v>
       </c>
       <c r="F292">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.25">
@@ -7223,7 +7223,7 @@
         <v>589</v>
       </c>
       <c r="F293">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.25">
@@ -7240,7 +7240,7 @@
         <v>590</v>
       </c>
       <c r="F294">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.25">
@@ -7257,7 +7257,7 @@
         <v>591</v>
       </c>
       <c r="F295">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.25">
@@ -7274,7 +7274,7 @@
         <v>592</v>
       </c>
       <c r="F296">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.25">
@@ -7291,7 +7291,7 @@
         <v>593</v>
       </c>
       <c r="F297">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>594</v>
       </c>
       <c r="F298">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.25">
@@ -7325,7 +7325,7 @@
         <v>595</v>
       </c>
       <c r="F299">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.25">
@@ -7342,7 +7342,7 @@
         <v>596</v>
       </c>
       <c r="F300">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.25">
@@ -7359,7 +7359,7 @@
         <v>597</v>
       </c>
       <c r="F301">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.25">
@@ -7376,7 +7376,7 @@
         <v>598</v>
       </c>
       <c r="F302">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>599</v>
       </c>
       <c r="F303">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.25">
@@ -7410,7 +7410,7 @@
         <v>600</v>
       </c>
       <c r="F304">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.25">
@@ -7427,7 +7427,7 @@
         <v>601</v>
       </c>
       <c r="F305">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.25">
@@ -7444,7 +7444,7 @@
         <v>602</v>
       </c>
       <c r="F306">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.25">
@@ -7461,7 +7461,7 @@
         <v>603</v>
       </c>
       <c r="F307">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.25">
@@ -7478,7 +7478,7 @@
         <v>604</v>
       </c>
       <c r="F308">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.25">
@@ -7495,7 +7495,7 @@
         <v>605</v>
       </c>
       <c r="F309">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.25">
@@ -7512,7 +7512,7 @@
         <v>606</v>
       </c>
       <c r="F310">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.25">
@@ -7529,7 +7529,7 @@
         <v>607</v>
       </c>
       <c r="F311">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.25">
@@ -7546,7 +7546,7 @@
         <v>608</v>
       </c>
       <c r="F312">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.25">
@@ -7563,7 +7563,7 @@
         <v>548</v>
       </c>
       <c r="F313">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>609</v>
       </c>
       <c r="F314">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.25">
@@ -7597,7 +7597,7 @@
         <v>610</v>
       </c>
       <c r="F315">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.25">
@@ -7614,7 +7614,7 @@
         <v>611</v>
       </c>
       <c r="F316">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.25">
@@ -7631,7 +7631,7 @@
         <v>612</v>
       </c>
       <c r="F317">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.25">
@@ -7648,7 +7648,7 @@
         <v>613</v>
       </c>
       <c r="F318">
-        <v>52</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
